--- a/industry/industry_config.xlsx
+++ b/industry/industry_config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fraunhofer-my.sharepoint.com/personal/rakesh_etikala_narendar_iee_fraunhofer_de/Documents/Desktop/sectoral-energy-demands/industry/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{32B99746-D61E-43DF-9653-52B59C7158BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FAD6AF4-4D8B-4C24-A81A-6BA76EF30A05}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{32B99746-D61E-43DF-9653-52B59C7158BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3115F34-CC2B-42F8-8F64-EFADADE3718B}"/>
   <bookViews>
-    <workbookView xWindow="7100" yWindow="2620" windowWidth="15330" windowHeight="11630" xr2:uid="{C5A233EC-3C33-42EA-837D-8F573F595C2A}"/>
+    <workbookView xWindow="2300" yWindow="2640" windowWidth="18630" windowHeight="15090" xr2:uid="{C5A233EC-3C33-42EA-837D-8F573F595C2A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1029,9 +1029,6 @@
       <c r="E2">
         <v>0</v>
       </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
     </row>
     <row r="3" spans="1:63" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
@@ -1049,9 +1046,6 @@
       <c r="E3">
         <v>0</v>
       </c>
-      <c r="R3">
-        <v>5.8500000000000003E-2</v>
-      </c>
     </row>
     <row r="4" spans="1:63" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
@@ -1069,9 +1063,6 @@
       <c r="E4">
         <v>0</v>
       </c>
-      <c r="R4">
-        <v>0.08</v>
-      </c>
     </row>
     <row r="5" spans="1:63" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
@@ -1089,9 +1080,6 @@
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
     </row>
     <row r="6" spans="1:63" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
@@ -1108,9 +1096,6 @@
       </c>
       <c r="E6">
         <v>0.01</v>
-      </c>
-      <c r="R6">
-        <v>5.8500000000000003E-2</v>
       </c>
     </row>
     <row r="7" spans="1:63" x14ac:dyDescent="0.35">

--- a/industry/industry_config.xlsx
+++ b/industry/industry_config.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fraunhofer-my.sharepoint.com/personal/rakesh_etikala_narendar_iee_fraunhofer_de/Documents/Desktop/sectoral-energy-demands/industry/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{32B99746-D61E-43DF-9653-52B59C7158BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3115F34-CC2B-42F8-8F64-EFADADE3718B}"/>
+  <xr:revisionPtr revIDLastSave="416" documentId="8_{32B99746-D61E-43DF-9653-52B59C7158BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{324DBD8E-748A-4698-8D41-2F459E65C2CF}"/>
   <bookViews>
-    <workbookView xWindow="2300" yWindow="2640" windowWidth="18630" windowHeight="15090" xr2:uid="{C5A233EC-3C33-42EA-837D-8F573F595C2A}"/>
+    <workbookView xWindow="18820" yWindow="1180" windowWidth="18710" windowHeight="15370" xr2:uid="{C5A233EC-3C33-42EA-837D-8F573F595C2A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$751</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2313" uniqueCount="193">
   <si>
     <t>Assumption Type</t>
   </si>
@@ -402,6 +405,219 @@
   </si>
   <si>
     <t>Energy Demand factor of Coal for unspecified non energy use</t>
+  </si>
+  <si>
+    <t>TECH_SHARE</t>
+  </si>
+  <si>
+    <t>Share of electricity for unspecified construction</t>
+  </si>
+  <si>
+    <t>Share of oil for unspecified construction</t>
+  </si>
+  <si>
+    <t>Share of gas for unspecified construction</t>
+  </si>
+  <si>
+    <t>Share of coal for unspecified construction</t>
+  </si>
+  <si>
+    <t>Share of biomass for unspecified construction</t>
+  </si>
+  <si>
+    <t>Share of hydrogen for unspecified construction</t>
+  </si>
+  <si>
+    <t>Share of ammonia for unspecified construction</t>
+  </si>
+  <si>
+    <t>Share of methanol for unspecified construction</t>
+  </si>
+  <si>
+    <t>Share of steel for unspecified construction</t>
+  </si>
+  <si>
+    <t>Final Energy of construction</t>
+  </si>
+  <si>
+    <t>Final Energy of food and tobacco</t>
+  </si>
+  <si>
+    <t>Share of oil for unspecified food and tobacco</t>
+  </si>
+  <si>
+    <t>Share of gas for unspecified food and tobacco</t>
+  </si>
+  <si>
+    <t>Share of electricity for unspecified food and tobacco</t>
+  </si>
+  <si>
+    <t>Share of coal for unspecified food and tobacco</t>
+  </si>
+  <si>
+    <t>Share of biomass for unspecified food and tobacco</t>
+  </si>
+  <si>
+    <t>Share of hydrogen for unspecified food and tobacco</t>
+  </si>
+  <si>
+    <t>Share of ammonia for unspecified food and tobacco</t>
+  </si>
+  <si>
+    <t>Share of methanol for unspecified food and tobacco</t>
+  </si>
+  <si>
+    <t>Share of steel for unspecified food and tobacco</t>
+  </si>
+  <si>
+    <t>Final Energy of machinery</t>
+  </si>
+  <si>
+    <t>Share of oil for unspecified machinery</t>
+  </si>
+  <si>
+    <t>Share of gas for unspecified machinery</t>
+  </si>
+  <si>
+    <t>Share of electricity for unspecified machinery</t>
+  </si>
+  <si>
+    <t>Share of coal for unspecified machinery</t>
+  </si>
+  <si>
+    <t>Share of biomass for unspecified machinery</t>
+  </si>
+  <si>
+    <t>Share of hydrogen for unspecified machinery</t>
+  </si>
+  <si>
+    <t>Share of ammonia for unspecified machinery</t>
+  </si>
+  <si>
+    <t>Share of methanol for unspecified machinery</t>
+  </si>
+  <si>
+    <t>Share of steel for unspecified machinery</t>
+  </si>
+  <si>
+    <t>Final Energy of mining and quarrying</t>
+  </si>
+  <si>
+    <t>Share of oil for unspecified mining and quarrying</t>
+  </si>
+  <si>
+    <t>Share of gas for unspecified mining and quarrying</t>
+  </si>
+  <si>
+    <t>Share of electricity for unspecified mining and quarrying</t>
+  </si>
+  <si>
+    <t>Share of coal for unspecified mining and quarrying</t>
+  </si>
+  <si>
+    <t>Share of biomass for unspecified mining and quarrying</t>
+  </si>
+  <si>
+    <t>Share of hydrogen for unspecified mining and quarrying</t>
+  </si>
+  <si>
+    <t>Share of ammonia for unspecified mining and quarrying</t>
+  </si>
+  <si>
+    <t>Share of methanol for unspecified mining and quarrying</t>
+  </si>
+  <si>
+    <t>Share of steel for unspecified mining and quarrying</t>
+  </si>
+  <si>
+    <t>Final Energy of textile and leather</t>
+  </si>
+  <si>
+    <t>Share of oil for unspecified textile and leather</t>
+  </si>
+  <si>
+    <t>Share of gas for unspecified textile and leather</t>
+  </si>
+  <si>
+    <t>Share of electricity for unspecified textile and leather</t>
+  </si>
+  <si>
+    <t>Share of coal for unspecified textile and leather</t>
+  </si>
+  <si>
+    <t>Share of biomass for unspecified textile and leather</t>
+  </si>
+  <si>
+    <t>Share of hydrogen for unspecified textile and leather</t>
+  </si>
+  <si>
+    <t>Share of ammonia for unspecified textile and leather</t>
+  </si>
+  <si>
+    <t>Share of methanol for unspecified textile and leather</t>
+  </si>
+  <si>
+    <t>Share of steel for unspecified textile and leather</t>
+  </si>
+  <si>
+    <t>Final Energy of transport equipment</t>
+  </si>
+  <si>
+    <t>Share of oil for unspecified transport equipment</t>
+  </si>
+  <si>
+    <t>Share of gas for unspecified transport equipment</t>
+  </si>
+  <si>
+    <t>Share of electricity for unspecified transport equipment</t>
+  </si>
+  <si>
+    <t>Share of coal for unspecified transport equipment</t>
+  </si>
+  <si>
+    <t>Share of biomass for unspecified transport equipment</t>
+  </si>
+  <si>
+    <t>Share of hydrogen for unspecified transport equipment</t>
+  </si>
+  <si>
+    <t>Share of ammonia for unspecified transport equipment</t>
+  </si>
+  <si>
+    <t>Share of methanol for unspecified transport equipment</t>
+  </si>
+  <si>
+    <t>Share of steel for unspecified transport equipment</t>
+  </si>
+  <si>
+    <t>Final Energy of wood and wood products</t>
+  </si>
+  <si>
+    <t>Share of oil for unspecified wood and wood products</t>
+  </si>
+  <si>
+    <t>Share of gas for unspecified wood and wood products</t>
+  </si>
+  <si>
+    <t>Share of electricity for unspecified wood and wood products</t>
+  </si>
+  <si>
+    <t>Share of coal for unspecified wood and wood products</t>
+  </si>
+  <si>
+    <t>Share of biomass for unspecified wood and wood products</t>
+  </si>
+  <si>
+    <t>Share of hydrogen for unspecified wood and wood products</t>
+  </si>
+  <si>
+    <t>Share of ammonia for unspecified wood and wood products</t>
+  </si>
+  <si>
+    <t>Share of methanol for unspecified wood and wood products</t>
+  </si>
+  <si>
+    <t>Share of steel for unspecified wood and wood products</t>
   </si>
 </sst>
 </file>
@@ -811,15 +1027,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E24C6E2-DFBD-4ECB-B058-D278CB417CB7}">
-  <dimension ref="A1:BK331"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:BK751"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.1796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="61.453125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.1796875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="17" width="0" hidden="1" customWidth="1"/>
+    <col min="6" max="17" width="8.7265625" hidden="1" customWidth="1"/>
     <col min="19" max="19" width="11" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="11.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:63" x14ac:dyDescent="0.35">
@@ -1030,7 +1251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:63" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:63" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>63</v>
       </c>
@@ -1047,7 +1268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:63" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:63" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>63</v>
       </c>
@@ -1081,7 +1302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:63" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:63" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>63</v>
       </c>
@@ -1098,7 +1319,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:63" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:63" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>63</v>
       </c>
@@ -1132,7 +1353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:63" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:63" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>63</v>
       </c>
@@ -1149,7 +1370,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="10" spans="1:63" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:63" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>63</v>
       </c>
@@ -1183,7 +1404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:63" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:63" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>63</v>
       </c>
@@ -1200,7 +1421,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="13" spans="1:63" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:63" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>63</v>
       </c>
@@ -1234,7 +1455,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="15" spans="1:63" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:63" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>63</v>
       </c>
@@ -1251,7 +1472,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="16" spans="1:63" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:63" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>63</v>
       </c>
@@ -1285,7 +1506,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>63</v>
       </c>
@@ -1302,7 +1523,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>63</v>
       </c>
@@ -1336,7 +1557,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>63</v>
       </c>
@@ -1353,7 +1574,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>63</v>
       </c>
@@ -1387,7 +1608,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>63</v>
       </c>
@@ -1404,7 +1625,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>63</v>
       </c>
@@ -1438,7 +1659,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -1455,7 +1676,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>63</v>
       </c>
@@ -1489,7 +1710,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -1506,7 +1727,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -1540,7 +1761,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>63</v>
       </c>
@@ -1557,7 +1778,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>63</v>
       </c>
@@ -1591,7 +1812,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>63</v>
       </c>
@@ -1608,7 +1829,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>63</v>
       </c>
@@ -1642,7 +1863,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>63</v>
       </c>
@@ -1659,7 +1880,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>63</v>
       </c>
@@ -1693,7 +1914,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>63</v>
       </c>
@@ -1710,7 +1931,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>63</v>
       </c>
@@ -1744,7 +1965,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>63</v>
       </c>
@@ -1761,7 +1982,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>63</v>
       </c>
@@ -1795,7 +2016,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>63</v>
       </c>
@@ -1812,7 +2033,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>63</v>
       </c>
@@ -1846,7 +2067,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>63</v>
       </c>
@@ -1863,7 +2084,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>63</v>
       </c>
@@ -1897,7 +2118,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>63</v>
       </c>
@@ -1914,7 +2135,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>63</v>
       </c>
@@ -1948,7 +2169,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>63</v>
       </c>
@@ -1965,7 +2186,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>63</v>
       </c>
@@ -1999,7 +2220,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>63</v>
       </c>
@@ -2016,7 +2237,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>63</v>
       </c>
@@ -2050,7 +2271,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>63</v>
       </c>
@@ -2067,7 +2288,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>63</v>
       </c>
@@ -2101,7 +2322,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>63</v>
       </c>
@@ -2118,7 +2339,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>63</v>
       </c>
@@ -2152,7 +2373,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>63</v>
       </c>
@@ -2169,7 +2390,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>63</v>
       </c>
@@ -2203,7 +2424,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>63</v>
       </c>
@@ -2220,7 +2441,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>63</v>
       </c>
@@ -2254,7 +2475,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>63</v>
       </c>
@@ -2271,7 +2492,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>63</v>
       </c>
@@ -2305,7 +2526,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>63</v>
       </c>
@@ -2322,7 +2543,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>63</v>
       </c>
@@ -2356,7 +2577,7 @@
         <v>-1.9E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>63</v>
       </c>
@@ -2373,7 +2594,7 @@
         <v>-1.9E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>63</v>
       </c>
@@ -2407,7 +2628,7 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>63</v>
       </c>
@@ -2424,7 +2645,7 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>63</v>
       </c>
@@ -2458,7 +2679,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>63</v>
       </c>
@@ -2475,7 +2696,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>63</v>
       </c>
@@ -2509,7 +2730,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>63</v>
       </c>
@@ -2526,7 +2747,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>63</v>
       </c>
@@ -2560,7 +2781,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>63</v>
       </c>
@@ -2577,7 +2798,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>63</v>
       </c>
@@ -2611,7 +2832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>63</v>
       </c>
@@ -2628,7 +2849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>63</v>
       </c>
@@ -2662,7 +2883,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>63</v>
       </c>
@@ -2679,7 +2900,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>63</v>
       </c>
@@ -2713,7 +2934,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>63</v>
       </c>
@@ -2730,7 +2951,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>63</v>
       </c>
@@ -2764,7 +2985,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>63</v>
       </c>
@@ -2781,7 +3002,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>63</v>
       </c>
@@ -2815,7 +3036,7 @@
         <v>-2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>63</v>
       </c>
@@ -2832,7 +3053,7 @@
         <v>-2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>63</v>
       </c>
@@ -2866,7 +3087,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>63</v>
       </c>
@@ -2883,7 +3104,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>63</v>
       </c>
@@ -2917,7 +3138,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>63</v>
       </c>
@@ -2934,7 +3155,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>63</v>
       </c>
@@ -2968,7 +3189,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>63</v>
       </c>
@@ -2985,7 +3206,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>63</v>
       </c>
@@ -3019,7 +3240,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>63</v>
       </c>
@@ -3036,7 +3257,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>63</v>
       </c>
@@ -3067,10 +3288,10 @@
         <v>65</v>
       </c>
       <c r="E122">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>63</v>
       </c>
@@ -3084,10 +3305,10 @@
         <v>66</v>
       </c>
       <c r="E123">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>63</v>
       </c>
@@ -3101,7 +3322,7 @@
         <v>67</v>
       </c>
       <c r="E124">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.35">
@@ -3118,10 +3339,10 @@
         <v>65</v>
       </c>
       <c r="E125">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>63</v>
       </c>
@@ -3135,10 +3356,10 @@
         <v>66</v>
       </c>
       <c r="E126">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>63</v>
       </c>
@@ -3152,7 +3373,7 @@
         <v>67</v>
       </c>
       <c r="E127">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.35">
@@ -3172,7 +3393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>63</v>
       </c>
@@ -3189,7 +3410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>63</v>
       </c>
@@ -3223,7 +3444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>63</v>
       </c>
@@ -3240,7 +3461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>63</v>
       </c>
@@ -3274,7 +3495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>63</v>
       </c>
@@ -3291,7 +3512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>63</v>
       </c>
@@ -3325,7 +3546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>63</v>
       </c>
@@ -3342,7 +3563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>63</v>
       </c>
@@ -3376,7 +3597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>63</v>
       </c>
@@ -3393,7 +3614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>63</v>
       </c>
@@ -3427,7 +3648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>63</v>
       </c>
@@ -3444,7 +3665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>63</v>
       </c>
@@ -3478,7 +3699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>63</v>
       </c>
@@ -3495,7 +3716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>63</v>
       </c>
@@ -3529,7 +3750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>63</v>
       </c>
@@ -3546,7 +3767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>63</v>
       </c>
@@ -3580,7 +3801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>63</v>
       </c>
@@ -3597,7 +3818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>63</v>
       </c>
@@ -3631,7 +3852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>63</v>
       </c>
@@ -3648,7 +3869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>63</v>
       </c>
@@ -3682,7 +3903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>63</v>
       </c>
@@ -3699,7 +3920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>63</v>
       </c>
@@ -3733,7 +3954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>63</v>
       </c>
@@ -3750,7 +3971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>63</v>
       </c>
@@ -3784,7 +4005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>63</v>
       </c>
@@ -3801,7 +4022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>63</v>
       </c>
@@ -3835,7 +4056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>63</v>
       </c>
@@ -3852,7 +4073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>63</v>
       </c>
@@ -3886,7 +4107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>63</v>
       </c>
@@ -3903,7 +4124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>63</v>
       </c>
@@ -3937,7 +4158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>63</v>
       </c>
@@ -3954,7 +4175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>63</v>
       </c>
@@ -3988,7 +4209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>63</v>
       </c>
@@ -4005,7 +4226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>63</v>
       </c>
@@ -4039,7 +4260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>63</v>
       </c>
@@ -4056,7 +4277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>63</v>
       </c>
@@ -4090,7 +4311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>63</v>
       </c>
@@ -4107,7 +4328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>63</v>
       </c>
@@ -4141,7 +4362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>63</v>
       </c>
@@ -4158,7 +4379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>63</v>
       </c>
@@ -4192,7 +4413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>63</v>
       </c>
@@ -4209,7 +4430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>63</v>
       </c>
@@ -4243,7 +4464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>63</v>
       </c>
@@ -4260,7 +4481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>63</v>
       </c>
@@ -4294,7 +4515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>63</v>
       </c>
@@ -4311,7 +4532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>63</v>
       </c>
@@ -4345,7 +4566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>63</v>
       </c>
@@ -4362,7 +4583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>63</v>
       </c>
@@ -4396,7 +4617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>63</v>
       </c>
@@ -4413,7 +4634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>63</v>
       </c>
@@ -4447,7 +4668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>63</v>
       </c>
@@ -4464,7 +4685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>63</v>
       </c>
@@ -4498,7 +4719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>63</v>
       </c>
@@ -4515,7 +4736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>63</v>
       </c>
@@ -4549,7 +4770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>63</v>
       </c>
@@ -4566,7 +4787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>63</v>
       </c>
@@ -4600,7 +4821,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>63</v>
       </c>
@@ -4617,7 +4838,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>63</v>
       </c>
@@ -4651,7 +4872,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>63</v>
       </c>
@@ -4668,7 +4889,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>63</v>
       </c>
@@ -4702,7 +4923,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>63</v>
       </c>
@@ -4719,7 +4940,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>63</v>
       </c>
@@ -4753,7 +4974,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>63</v>
       </c>
@@ -4770,7 +4991,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>63</v>
       </c>
@@ -4804,7 +5025,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>63</v>
       </c>
@@ -4821,7 +5042,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>63</v>
       </c>
@@ -4855,7 +5076,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>63</v>
       </c>
@@ -4872,7 +5093,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>63</v>
       </c>
@@ -4906,7 +5127,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>63</v>
       </c>
@@ -4923,7 +5144,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>63</v>
       </c>
@@ -4957,7 +5178,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>63</v>
       </c>
@@ -4974,7 +5195,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>63</v>
       </c>
@@ -5008,7 +5229,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>63</v>
       </c>
@@ -5025,7 +5246,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>63</v>
       </c>
@@ -5059,7 +5280,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>63</v>
       </c>
@@ -5076,7 +5297,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>63</v>
       </c>
@@ -5110,7 +5331,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>63</v>
       </c>
@@ -5127,7 +5348,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>63</v>
       </c>
@@ -5161,7 +5382,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>63</v>
       </c>
@@ -5178,7 +5399,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>63</v>
       </c>
@@ -5212,7 +5433,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>63</v>
       </c>
@@ -5229,7 +5450,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>63</v>
       </c>
@@ -5263,7 +5484,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>63</v>
       </c>
@@ -5280,7 +5501,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>63</v>
       </c>
@@ -5314,7 +5535,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>63</v>
       </c>
@@ -5331,7 +5552,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>63</v>
       </c>
@@ -5365,7 +5586,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>63</v>
       </c>
@@ -5382,7 +5603,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>63</v>
       </c>
@@ -5416,7 +5637,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>63</v>
       </c>
@@ -5433,7 +5654,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>63</v>
       </c>
@@ -5467,7 +5688,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>63</v>
       </c>
@@ -5484,7 +5705,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>63</v>
       </c>
@@ -5518,7 +5739,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>63</v>
       </c>
@@ -5535,7 +5756,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>63</v>
       </c>
@@ -5569,7 +5790,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>63</v>
       </c>
@@ -5586,7 +5807,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>63</v>
       </c>
@@ -5620,7 +5841,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>63</v>
       </c>
@@ -5637,7 +5858,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>63</v>
       </c>
@@ -5671,7 +5892,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>63</v>
       </c>
@@ -5688,7 +5909,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>63</v>
       </c>
@@ -5722,7 +5943,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>63</v>
       </c>
@@ -5739,7 +5960,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>63</v>
       </c>
@@ -5773,7 +5994,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>63</v>
       </c>
@@ -5790,7 +6011,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>63</v>
       </c>
@@ -5824,7 +6045,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>63</v>
       </c>
@@ -5841,7 +6062,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>63</v>
       </c>
@@ -5875,7 +6096,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>63</v>
       </c>
@@ -5892,7 +6113,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>63</v>
       </c>
@@ -5926,7 +6147,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>63</v>
       </c>
@@ -5943,7 +6164,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>63</v>
       </c>
@@ -5977,7 +6198,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>63</v>
       </c>
@@ -5994,7 +6215,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>63</v>
       </c>
@@ -6028,7 +6249,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>63</v>
       </c>
@@ -6045,7 +6266,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>63</v>
       </c>
@@ -6079,7 +6300,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>63</v>
       </c>
@@ -6096,7 +6317,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>63</v>
       </c>
@@ -6130,7 +6351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>63</v>
       </c>
@@ -6147,7 +6368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>63</v>
       </c>
@@ -6181,7 +6402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>63</v>
       </c>
@@ -6198,7 +6419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>63</v>
       </c>
@@ -6232,7 +6453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>63</v>
       </c>
@@ -6249,7 +6470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>63</v>
       </c>
@@ -6283,7 +6504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>63</v>
       </c>
@@ -6300,7 +6521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>63</v>
       </c>
@@ -6334,7 +6555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>63</v>
       </c>
@@ -6351,7 +6572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>63</v>
       </c>
@@ -6385,7 +6606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>63</v>
       </c>
@@ -6402,7 +6623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>63</v>
       </c>
@@ -6436,7 +6657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>63</v>
       </c>
@@ -6453,7 +6674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>63</v>
       </c>
@@ -6470,7 +6691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>63</v>
       </c>
@@ -6487,7 +6708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>63</v>
       </c>
@@ -6504,7 +6725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>63</v>
       </c>
@@ -6521,7 +6742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>63</v>
       </c>
@@ -6538,7 +6759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>63</v>
       </c>
@@ -6555,7 +6776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>63</v>
       </c>
@@ -6572,7 +6793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>63</v>
       </c>
@@ -6589,7 +6810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>63</v>
       </c>
@@ -6606,7 +6827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>63</v>
       </c>
@@ -6623,7 +6844,7190 @@
         <v>0</v>
       </c>
     </row>
+    <row r="332" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A332" t="s">
+        <v>63</v>
+      </c>
+      <c r="B332" t="s">
+        <v>132</v>
+      </c>
+      <c r="C332">
+        <v>2030</v>
+      </c>
+      <c r="D332" t="s">
+        <v>65</v>
+      </c>
+      <c r="E332">
+        <v>0.01</v>
+      </c>
+      <c r="R332">
+        <v>2.9000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="333" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A333" t="s">
+        <v>63</v>
+      </c>
+      <c r="B333" t="s">
+        <v>132</v>
+      </c>
+      <c r="C333">
+        <v>2030</v>
+      </c>
+      <c r="D333" t="s">
+        <v>66</v>
+      </c>
+      <c r="E333">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="334" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A334" t="s">
+        <v>63</v>
+      </c>
+      <c r="B334" t="s">
+        <v>132</v>
+      </c>
+      <c r="C334">
+        <v>2030</v>
+      </c>
+      <c r="D334" t="s">
+        <v>67</v>
+      </c>
+      <c r="E334">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="335" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A335" t="s">
+        <v>63</v>
+      </c>
+      <c r="B335" t="s">
+        <v>132</v>
+      </c>
+      <c r="C335">
+        <v>2050</v>
+      </c>
+      <c r="D335" t="s">
+        <v>65</v>
+      </c>
+      <c r="E335">
+        <v>0.04</v>
+      </c>
+      <c r="R335">
+        <v>2.9000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="336" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A336" t="s">
+        <v>63</v>
+      </c>
+      <c r="B336" t="s">
+        <v>132</v>
+      </c>
+      <c r="C336">
+        <v>2050</v>
+      </c>
+      <c r="D336" t="s">
+        <v>66</v>
+      </c>
+      <c r="E336">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A337" t="s">
+        <v>63</v>
+      </c>
+      <c r="B337" t="s">
+        <v>132</v>
+      </c>
+      <c r="C337">
+        <v>2050</v>
+      </c>
+      <c r="D337" t="s">
+        <v>67</v>
+      </c>
+      <c r="E337">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A338" t="s">
+        <v>122</v>
+      </c>
+      <c r="B338" t="s">
+        <v>123</v>
+      </c>
+      <c r="C338">
+        <v>2030</v>
+      </c>
+      <c r="D338" t="s">
+        <v>65</v>
+      </c>
+      <c r="E338">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A339" t="s">
+        <v>122</v>
+      </c>
+      <c r="B339" t="s">
+        <v>123</v>
+      </c>
+      <c r="C339">
+        <v>2030</v>
+      </c>
+      <c r="D339" t="s">
+        <v>66</v>
+      </c>
+      <c r="E339">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A340" t="s">
+        <v>122</v>
+      </c>
+      <c r="B340" t="s">
+        <v>123</v>
+      </c>
+      <c r="C340">
+        <v>2030</v>
+      </c>
+      <c r="D340" t="s">
+        <v>67</v>
+      </c>
+      <c r="E340">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A341" t="s">
+        <v>122</v>
+      </c>
+      <c r="B341" t="s">
+        <v>123</v>
+      </c>
+      <c r="C341">
+        <v>2050</v>
+      </c>
+      <c r="D341" t="s">
+        <v>65</v>
+      </c>
+      <c r="E341">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A342" t="s">
+        <v>122</v>
+      </c>
+      <c r="B342" t="s">
+        <v>123</v>
+      </c>
+      <c r="C342">
+        <v>2050</v>
+      </c>
+      <c r="D342" t="s">
+        <v>66</v>
+      </c>
+      <c r="E342">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A343" t="s">
+        <v>122</v>
+      </c>
+      <c r="B343" t="s">
+        <v>123</v>
+      </c>
+      <c r="C343">
+        <v>2050</v>
+      </c>
+      <c r="D343" t="s">
+        <v>67</v>
+      </c>
+      <c r="E343">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A344" t="s">
+        <v>122</v>
+      </c>
+      <c r="B344" t="s">
+        <v>124</v>
+      </c>
+      <c r="C344">
+        <v>2030</v>
+      </c>
+      <c r="D344" t="s">
+        <v>65</v>
+      </c>
+      <c r="E344">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A345" t="s">
+        <v>122</v>
+      </c>
+      <c r="B345" t="s">
+        <v>124</v>
+      </c>
+      <c r="C345">
+        <v>2030</v>
+      </c>
+      <c r="D345" t="s">
+        <v>66</v>
+      </c>
+      <c r="E345">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A346" t="s">
+        <v>122</v>
+      </c>
+      <c r="B346" t="s">
+        <v>124</v>
+      </c>
+      <c r="C346">
+        <v>2030</v>
+      </c>
+      <c r="D346" t="s">
+        <v>67</v>
+      </c>
+      <c r="E346">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A347" t="s">
+        <v>122</v>
+      </c>
+      <c r="B347" t="s">
+        <v>124</v>
+      </c>
+      <c r="C347">
+        <v>2050</v>
+      </c>
+      <c r="D347" t="s">
+        <v>65</v>
+      </c>
+      <c r="E347">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A348" t="s">
+        <v>122</v>
+      </c>
+      <c r="B348" t="s">
+        <v>124</v>
+      </c>
+      <c r="C348">
+        <v>2050</v>
+      </c>
+      <c r="D348" t="s">
+        <v>66</v>
+      </c>
+      <c r="E348">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A349" t="s">
+        <v>122</v>
+      </c>
+      <c r="B349" t="s">
+        <v>124</v>
+      </c>
+      <c r="C349">
+        <v>2050</v>
+      </c>
+      <c r="D349" t="s">
+        <v>67</v>
+      </c>
+      <c r="E349">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A350" t="s">
+        <v>122</v>
+      </c>
+      <c r="B350" t="s">
+        <v>125</v>
+      </c>
+      <c r="C350">
+        <v>2030</v>
+      </c>
+      <c r="D350" t="s">
+        <v>65</v>
+      </c>
+      <c r="E350">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A351" t="s">
+        <v>122</v>
+      </c>
+      <c r="B351" t="s">
+        <v>125</v>
+      </c>
+      <c r="C351">
+        <v>2030</v>
+      </c>
+      <c r="D351" t="s">
+        <v>66</v>
+      </c>
+      <c r="E351">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A352" t="s">
+        <v>122</v>
+      </c>
+      <c r="B352" t="s">
+        <v>125</v>
+      </c>
+      <c r="C352">
+        <v>2030</v>
+      </c>
+      <c r="D352" t="s">
+        <v>67</v>
+      </c>
+      <c r="E352">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A353" t="s">
+        <v>122</v>
+      </c>
+      <c r="B353" t="s">
+        <v>125</v>
+      </c>
+      <c r="C353">
+        <v>2050</v>
+      </c>
+      <c r="D353" t="s">
+        <v>65</v>
+      </c>
+      <c r="E353">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A354" t="s">
+        <v>122</v>
+      </c>
+      <c r="B354" t="s">
+        <v>125</v>
+      </c>
+      <c r="C354">
+        <v>2050</v>
+      </c>
+      <c r="D354" t="s">
+        <v>66</v>
+      </c>
+      <c r="E354">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A355" t="s">
+        <v>122</v>
+      </c>
+      <c r="B355" t="s">
+        <v>125</v>
+      </c>
+      <c r="C355">
+        <v>2050</v>
+      </c>
+      <c r="D355" t="s">
+        <v>67</v>
+      </c>
+      <c r="E355">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A356" t="s">
+        <v>122</v>
+      </c>
+      <c r="B356" t="s">
+        <v>126</v>
+      </c>
+      <c r="C356">
+        <v>2030</v>
+      </c>
+      <c r="D356" t="s">
+        <v>65</v>
+      </c>
+      <c r="E356">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A357" t="s">
+        <v>122</v>
+      </c>
+      <c r="B357" t="s">
+        <v>126</v>
+      </c>
+      <c r="C357">
+        <v>2030</v>
+      </c>
+      <c r="D357" t="s">
+        <v>66</v>
+      </c>
+      <c r="E357">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A358" t="s">
+        <v>122</v>
+      </c>
+      <c r="B358" t="s">
+        <v>126</v>
+      </c>
+      <c r="C358">
+        <v>2030</v>
+      </c>
+      <c r="D358" t="s">
+        <v>67</v>
+      </c>
+      <c r="E358">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A359" t="s">
+        <v>122</v>
+      </c>
+      <c r="B359" t="s">
+        <v>126</v>
+      </c>
+      <c r="C359">
+        <v>2050</v>
+      </c>
+      <c r="D359" t="s">
+        <v>65</v>
+      </c>
+      <c r="E359">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A360" t="s">
+        <v>122</v>
+      </c>
+      <c r="B360" t="s">
+        <v>126</v>
+      </c>
+      <c r="C360">
+        <v>2050</v>
+      </c>
+      <c r="D360" t="s">
+        <v>66</v>
+      </c>
+      <c r="E360">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A361" t="s">
+        <v>122</v>
+      </c>
+      <c r="B361" t="s">
+        <v>126</v>
+      </c>
+      <c r="C361">
+        <v>2050</v>
+      </c>
+      <c r="D361" t="s">
+        <v>67</v>
+      </c>
+      <c r="E361">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A362" t="s">
+        <v>122</v>
+      </c>
+      <c r="B362" t="s">
+        <v>127</v>
+      </c>
+      <c r="C362">
+        <v>2030</v>
+      </c>
+      <c r="D362" t="s">
+        <v>65</v>
+      </c>
+      <c r="E362">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A363" t="s">
+        <v>122</v>
+      </c>
+      <c r="B363" t="s">
+        <v>127</v>
+      </c>
+      <c r="C363">
+        <v>2030</v>
+      </c>
+      <c r="D363" t="s">
+        <v>66</v>
+      </c>
+      <c r="E363">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A364" t="s">
+        <v>122</v>
+      </c>
+      <c r="B364" t="s">
+        <v>127</v>
+      </c>
+      <c r="C364">
+        <v>2030</v>
+      </c>
+      <c r="D364" t="s">
+        <v>67</v>
+      </c>
+      <c r="E364">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A365" t="s">
+        <v>122</v>
+      </c>
+      <c r="B365" t="s">
+        <v>127</v>
+      </c>
+      <c r="C365">
+        <v>2050</v>
+      </c>
+      <c r="D365" t="s">
+        <v>65</v>
+      </c>
+      <c r="E365">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A366" t="s">
+        <v>122</v>
+      </c>
+      <c r="B366" t="s">
+        <v>127</v>
+      </c>
+      <c r="C366">
+        <v>2050</v>
+      </c>
+      <c r="D366" t="s">
+        <v>66</v>
+      </c>
+      <c r="E366">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A367" t="s">
+        <v>122</v>
+      </c>
+      <c r="B367" t="s">
+        <v>127</v>
+      </c>
+      <c r="C367">
+        <v>2050</v>
+      </c>
+      <c r="D367" t="s">
+        <v>67</v>
+      </c>
+      <c r="E367">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A368" t="s">
+        <v>122</v>
+      </c>
+      <c r="B368" t="s">
+        <v>128</v>
+      </c>
+      <c r="C368">
+        <v>2030</v>
+      </c>
+      <c r="D368" t="s">
+        <v>65</v>
+      </c>
+      <c r="E368">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A369" t="s">
+        <v>122</v>
+      </c>
+      <c r="B369" t="s">
+        <v>128</v>
+      </c>
+      <c r="C369">
+        <v>2030</v>
+      </c>
+      <c r="D369" t="s">
+        <v>66</v>
+      </c>
+      <c r="E369">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A370" t="s">
+        <v>122</v>
+      </c>
+      <c r="B370" t="s">
+        <v>128</v>
+      </c>
+      <c r="C370">
+        <v>2030</v>
+      </c>
+      <c r="D370" t="s">
+        <v>67</v>
+      </c>
+      <c r="E370">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A371" t="s">
+        <v>122</v>
+      </c>
+      <c r="B371" t="s">
+        <v>128</v>
+      </c>
+      <c r="C371">
+        <v>2050</v>
+      </c>
+      <c r="D371" t="s">
+        <v>65</v>
+      </c>
+      <c r="E371">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A372" t="s">
+        <v>122</v>
+      </c>
+      <c r="B372" t="s">
+        <v>128</v>
+      </c>
+      <c r="C372">
+        <v>2050</v>
+      </c>
+      <c r="D372" t="s">
+        <v>66</v>
+      </c>
+      <c r="E372">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A373" t="s">
+        <v>122</v>
+      </c>
+      <c r="B373" t="s">
+        <v>128</v>
+      </c>
+      <c r="C373">
+        <v>2050</v>
+      </c>
+      <c r="D373" t="s">
+        <v>67</v>
+      </c>
+      <c r="E373">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A374" t="s">
+        <v>122</v>
+      </c>
+      <c r="B374" t="s">
+        <v>129</v>
+      </c>
+      <c r="C374">
+        <v>2030</v>
+      </c>
+      <c r="D374" t="s">
+        <v>65</v>
+      </c>
+      <c r="E374">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A375" t="s">
+        <v>122</v>
+      </c>
+      <c r="B375" t="s">
+        <v>129</v>
+      </c>
+      <c r="C375">
+        <v>2030</v>
+      </c>
+      <c r="D375" t="s">
+        <v>66</v>
+      </c>
+      <c r="E375">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A376" t="s">
+        <v>122</v>
+      </c>
+      <c r="B376" t="s">
+        <v>129</v>
+      </c>
+      <c r="C376">
+        <v>2030</v>
+      </c>
+      <c r="D376" t="s">
+        <v>67</v>
+      </c>
+      <c r="E376">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A377" t="s">
+        <v>122</v>
+      </c>
+      <c r="B377" t="s">
+        <v>129</v>
+      </c>
+      <c r="C377">
+        <v>2050</v>
+      </c>
+      <c r="D377" t="s">
+        <v>65</v>
+      </c>
+      <c r="E377">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A378" t="s">
+        <v>122</v>
+      </c>
+      <c r="B378" t="s">
+        <v>129</v>
+      </c>
+      <c r="C378">
+        <v>2050</v>
+      </c>
+      <c r="D378" t="s">
+        <v>66</v>
+      </c>
+      <c r="E378">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A379" t="s">
+        <v>122</v>
+      </c>
+      <c r="B379" t="s">
+        <v>129</v>
+      </c>
+      <c r="C379">
+        <v>2050</v>
+      </c>
+      <c r="D379" t="s">
+        <v>67</v>
+      </c>
+      <c r="E379">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A380" t="s">
+        <v>122</v>
+      </c>
+      <c r="B380" t="s">
+        <v>130</v>
+      </c>
+      <c r="C380">
+        <v>2030</v>
+      </c>
+      <c r="D380" t="s">
+        <v>65</v>
+      </c>
+      <c r="E380">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A381" t="s">
+        <v>122</v>
+      </c>
+      <c r="B381" t="s">
+        <v>130</v>
+      </c>
+      <c r="C381">
+        <v>2030</v>
+      </c>
+      <c r="D381" t="s">
+        <v>66</v>
+      </c>
+      <c r="E381">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A382" t="s">
+        <v>122</v>
+      </c>
+      <c r="B382" t="s">
+        <v>130</v>
+      </c>
+      <c r="C382">
+        <v>2030</v>
+      </c>
+      <c r="D382" t="s">
+        <v>67</v>
+      </c>
+      <c r="E382">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A383" t="s">
+        <v>122</v>
+      </c>
+      <c r="B383" t="s">
+        <v>130</v>
+      </c>
+      <c r="C383">
+        <v>2050</v>
+      </c>
+      <c r="D383" t="s">
+        <v>65</v>
+      </c>
+      <c r="E383">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A384" t="s">
+        <v>122</v>
+      </c>
+      <c r="B384" t="s">
+        <v>130</v>
+      </c>
+      <c r="C384">
+        <v>2050</v>
+      </c>
+      <c r="D384" t="s">
+        <v>66</v>
+      </c>
+      <c r="E384">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A385" t="s">
+        <v>122</v>
+      </c>
+      <c r="B385" t="s">
+        <v>130</v>
+      </c>
+      <c r="C385">
+        <v>2050</v>
+      </c>
+      <c r="D385" t="s">
+        <v>67</v>
+      </c>
+      <c r="E385">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A386" t="s">
+        <v>122</v>
+      </c>
+      <c r="B386" t="s">
+        <v>131</v>
+      </c>
+      <c r="C386">
+        <v>2030</v>
+      </c>
+      <c r="D386" t="s">
+        <v>65</v>
+      </c>
+      <c r="E386">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A387" t="s">
+        <v>122</v>
+      </c>
+      <c r="B387" t="s">
+        <v>131</v>
+      </c>
+      <c r="C387">
+        <v>2030</v>
+      </c>
+      <c r="D387" t="s">
+        <v>66</v>
+      </c>
+      <c r="E387">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A388" t="s">
+        <v>122</v>
+      </c>
+      <c r="B388" t="s">
+        <v>131</v>
+      </c>
+      <c r="C388">
+        <v>2030</v>
+      </c>
+      <c r="D388" t="s">
+        <v>67</v>
+      </c>
+      <c r="E388">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A389" t="s">
+        <v>122</v>
+      </c>
+      <c r="B389" t="s">
+        <v>131</v>
+      </c>
+      <c r="C389">
+        <v>2050</v>
+      </c>
+      <c r="D389" t="s">
+        <v>65</v>
+      </c>
+      <c r="E389">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A390" t="s">
+        <v>122</v>
+      </c>
+      <c r="B390" t="s">
+        <v>131</v>
+      </c>
+      <c r="C390">
+        <v>2050</v>
+      </c>
+      <c r="D390" t="s">
+        <v>66</v>
+      </c>
+      <c r="E390">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A391" t="s">
+        <v>122</v>
+      </c>
+      <c r="B391" t="s">
+        <v>131</v>
+      </c>
+      <c r="C391">
+        <v>2050</v>
+      </c>
+      <c r="D391" t="s">
+        <v>67</v>
+      </c>
+      <c r="E391">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A392" t="s">
+        <v>63</v>
+      </c>
+      <c r="B392" t="s">
+        <v>133</v>
+      </c>
+      <c r="C392">
+        <v>2030</v>
+      </c>
+      <c r="D392" t="s">
+        <v>65</v>
+      </c>
+      <c r="E392">
+        <v>0</v>
+      </c>
+      <c r="R392">
+        <v>4.9000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="393" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A393" t="s">
+        <v>63</v>
+      </c>
+      <c r="B393" t="s">
+        <v>133</v>
+      </c>
+      <c r="C393">
+        <v>2030</v>
+      </c>
+      <c r="D393" t="s">
+        <v>66</v>
+      </c>
+      <c r="E393">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A394" t="s">
+        <v>63</v>
+      </c>
+      <c r="B394" t="s">
+        <v>133</v>
+      </c>
+      <c r="C394">
+        <v>2030</v>
+      </c>
+      <c r="D394" t="s">
+        <v>67</v>
+      </c>
+      <c r="E394">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A395" t="s">
+        <v>63</v>
+      </c>
+      <c r="B395" t="s">
+        <v>133</v>
+      </c>
+      <c r="C395">
+        <v>2050</v>
+      </c>
+      <c r="D395" t="s">
+        <v>65</v>
+      </c>
+      <c r="E395">
+        <v>0</v>
+      </c>
+      <c r="R395">
+        <v>4.9000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="396" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A396" t="s">
+        <v>63</v>
+      </c>
+      <c r="B396" t="s">
+        <v>133</v>
+      </c>
+      <c r="C396">
+        <v>2050</v>
+      </c>
+      <c r="D396" t="s">
+        <v>66</v>
+      </c>
+      <c r="E396">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A397" t="s">
+        <v>63</v>
+      </c>
+      <c r="B397" t="s">
+        <v>133</v>
+      </c>
+      <c r="C397">
+        <v>2050</v>
+      </c>
+      <c r="D397" t="s">
+        <v>67</v>
+      </c>
+      <c r="E397">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A398" t="s">
+        <v>122</v>
+      </c>
+      <c r="B398" t="s">
+        <v>134</v>
+      </c>
+      <c r="C398">
+        <v>2030</v>
+      </c>
+      <c r="D398" t="s">
+        <v>65</v>
+      </c>
+      <c r="E398">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A399" t="s">
+        <v>122</v>
+      </c>
+      <c r="B399" t="s">
+        <v>134</v>
+      </c>
+      <c r="C399">
+        <v>2030</v>
+      </c>
+      <c r="D399" t="s">
+        <v>66</v>
+      </c>
+      <c r="E399">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A400" t="s">
+        <v>122</v>
+      </c>
+      <c r="B400" t="s">
+        <v>134</v>
+      </c>
+      <c r="C400">
+        <v>2030</v>
+      </c>
+      <c r="D400" t="s">
+        <v>67</v>
+      </c>
+      <c r="E400">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A401" t="s">
+        <v>122</v>
+      </c>
+      <c r="B401" t="s">
+        <v>134</v>
+      </c>
+      <c r="C401">
+        <v>2050</v>
+      </c>
+      <c r="D401" t="s">
+        <v>65</v>
+      </c>
+      <c r="E401">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A402" t="s">
+        <v>122</v>
+      </c>
+      <c r="B402" t="s">
+        <v>134</v>
+      </c>
+      <c r="C402">
+        <v>2050</v>
+      </c>
+      <c r="D402" t="s">
+        <v>66</v>
+      </c>
+      <c r="E402">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A403" t="s">
+        <v>122</v>
+      </c>
+      <c r="B403" t="s">
+        <v>134</v>
+      </c>
+      <c r="C403">
+        <v>2050</v>
+      </c>
+      <c r="D403" t="s">
+        <v>67</v>
+      </c>
+      <c r="E403">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A404" t="s">
+        <v>122</v>
+      </c>
+      <c r="B404" t="s">
+        <v>135</v>
+      </c>
+      <c r="C404">
+        <v>2030</v>
+      </c>
+      <c r="D404" t="s">
+        <v>65</v>
+      </c>
+      <c r="E404">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A405" t="s">
+        <v>122</v>
+      </c>
+      <c r="B405" t="s">
+        <v>135</v>
+      </c>
+      <c r="C405">
+        <v>2030</v>
+      </c>
+      <c r="D405" t="s">
+        <v>66</v>
+      </c>
+      <c r="E405">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A406" t="s">
+        <v>122</v>
+      </c>
+      <c r="B406" t="s">
+        <v>135</v>
+      </c>
+      <c r="C406">
+        <v>2030</v>
+      </c>
+      <c r="D406" t="s">
+        <v>67</v>
+      </c>
+      <c r="E406">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A407" t="s">
+        <v>122</v>
+      </c>
+      <c r="B407" t="s">
+        <v>135</v>
+      </c>
+      <c r="C407">
+        <v>2050</v>
+      </c>
+      <c r="D407" t="s">
+        <v>65</v>
+      </c>
+      <c r="E407">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A408" t="s">
+        <v>122</v>
+      </c>
+      <c r="B408" t="s">
+        <v>135</v>
+      </c>
+      <c r="C408">
+        <v>2050</v>
+      </c>
+      <c r="D408" t="s">
+        <v>66</v>
+      </c>
+      <c r="E408">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A409" t="s">
+        <v>122</v>
+      </c>
+      <c r="B409" t="s">
+        <v>135</v>
+      </c>
+      <c r="C409">
+        <v>2050</v>
+      </c>
+      <c r="D409" t="s">
+        <v>67</v>
+      </c>
+      <c r="E409">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A410" t="s">
+        <v>122</v>
+      </c>
+      <c r="B410" t="s">
+        <v>136</v>
+      </c>
+      <c r="C410">
+        <v>2030</v>
+      </c>
+      <c r="D410" t="s">
+        <v>65</v>
+      </c>
+      <c r="E410">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A411" t="s">
+        <v>122</v>
+      </c>
+      <c r="B411" t="s">
+        <v>136</v>
+      </c>
+      <c r="C411">
+        <v>2030</v>
+      </c>
+      <c r="D411" t="s">
+        <v>66</v>
+      </c>
+      <c r="E411">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A412" t="s">
+        <v>122</v>
+      </c>
+      <c r="B412" t="s">
+        <v>136</v>
+      </c>
+      <c r="C412">
+        <v>2030</v>
+      </c>
+      <c r="D412" t="s">
+        <v>67</v>
+      </c>
+      <c r="E412">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A413" t="s">
+        <v>122</v>
+      </c>
+      <c r="B413" t="s">
+        <v>136</v>
+      </c>
+      <c r="C413">
+        <v>2050</v>
+      </c>
+      <c r="D413" t="s">
+        <v>65</v>
+      </c>
+      <c r="E413">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A414" t="s">
+        <v>122</v>
+      </c>
+      <c r="B414" t="s">
+        <v>136</v>
+      </c>
+      <c r="C414">
+        <v>2050</v>
+      </c>
+      <c r="D414" t="s">
+        <v>66</v>
+      </c>
+      <c r="E414">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A415" t="s">
+        <v>122</v>
+      </c>
+      <c r="B415" t="s">
+        <v>136</v>
+      </c>
+      <c r="C415">
+        <v>2050</v>
+      </c>
+      <c r="D415" t="s">
+        <v>67</v>
+      </c>
+      <c r="E415">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A416" t="s">
+        <v>122</v>
+      </c>
+      <c r="B416" t="s">
+        <v>137</v>
+      </c>
+      <c r="C416">
+        <v>2030</v>
+      </c>
+      <c r="D416" t="s">
+        <v>65</v>
+      </c>
+      <c r="E416">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A417" t="s">
+        <v>122</v>
+      </c>
+      <c r="B417" t="s">
+        <v>137</v>
+      </c>
+      <c r="C417">
+        <v>2030</v>
+      </c>
+      <c r="D417" t="s">
+        <v>66</v>
+      </c>
+      <c r="E417">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A418" t="s">
+        <v>122</v>
+      </c>
+      <c r="B418" t="s">
+        <v>137</v>
+      </c>
+      <c r="C418">
+        <v>2030</v>
+      </c>
+      <c r="D418" t="s">
+        <v>67</v>
+      </c>
+      <c r="E418">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A419" t="s">
+        <v>122</v>
+      </c>
+      <c r="B419" t="s">
+        <v>137</v>
+      </c>
+      <c r="C419">
+        <v>2050</v>
+      </c>
+      <c r="D419" t="s">
+        <v>65</v>
+      </c>
+      <c r="E419">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A420" t="s">
+        <v>122</v>
+      </c>
+      <c r="B420" t="s">
+        <v>137</v>
+      </c>
+      <c r="C420">
+        <v>2050</v>
+      </c>
+      <c r="D420" t="s">
+        <v>66</v>
+      </c>
+      <c r="E420">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A421" t="s">
+        <v>122</v>
+      </c>
+      <c r="B421" t="s">
+        <v>137</v>
+      </c>
+      <c r="C421">
+        <v>2050</v>
+      </c>
+      <c r="D421" t="s">
+        <v>67</v>
+      </c>
+      <c r="E421">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A422" t="s">
+        <v>122</v>
+      </c>
+      <c r="B422" t="s">
+        <v>138</v>
+      </c>
+      <c r="C422">
+        <v>2030</v>
+      </c>
+      <c r="D422" t="s">
+        <v>65</v>
+      </c>
+      <c r="E422">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A423" t="s">
+        <v>122</v>
+      </c>
+      <c r="B423" t="s">
+        <v>138</v>
+      </c>
+      <c r="C423">
+        <v>2030</v>
+      </c>
+      <c r="D423" t="s">
+        <v>66</v>
+      </c>
+      <c r="E423">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A424" t="s">
+        <v>122</v>
+      </c>
+      <c r="B424" t="s">
+        <v>138</v>
+      </c>
+      <c r="C424">
+        <v>2030</v>
+      </c>
+      <c r="D424" t="s">
+        <v>67</v>
+      </c>
+      <c r="E424">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A425" t="s">
+        <v>122</v>
+      </c>
+      <c r="B425" t="s">
+        <v>138</v>
+      </c>
+      <c r="C425">
+        <v>2050</v>
+      </c>
+      <c r="D425" t="s">
+        <v>65</v>
+      </c>
+      <c r="E425">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A426" t="s">
+        <v>122</v>
+      </c>
+      <c r="B426" t="s">
+        <v>138</v>
+      </c>
+      <c r="C426">
+        <v>2050</v>
+      </c>
+      <c r="D426" t="s">
+        <v>66</v>
+      </c>
+      <c r="E426">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A427" t="s">
+        <v>122</v>
+      </c>
+      <c r="B427" t="s">
+        <v>138</v>
+      </c>
+      <c r="C427">
+        <v>2050</v>
+      </c>
+      <c r="D427" t="s">
+        <v>67</v>
+      </c>
+      <c r="E427">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A428" t="s">
+        <v>122</v>
+      </c>
+      <c r="B428" t="s">
+        <v>139</v>
+      </c>
+      <c r="C428">
+        <v>2030</v>
+      </c>
+      <c r="D428" t="s">
+        <v>65</v>
+      </c>
+      <c r="E428">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A429" t="s">
+        <v>122</v>
+      </c>
+      <c r="B429" t="s">
+        <v>139</v>
+      </c>
+      <c r="C429">
+        <v>2030</v>
+      </c>
+      <c r="D429" t="s">
+        <v>66</v>
+      </c>
+      <c r="E429">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A430" t="s">
+        <v>122</v>
+      </c>
+      <c r="B430" t="s">
+        <v>139</v>
+      </c>
+      <c r="C430">
+        <v>2030</v>
+      </c>
+      <c r="D430" t="s">
+        <v>67</v>
+      </c>
+      <c r="E430">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A431" t="s">
+        <v>122</v>
+      </c>
+      <c r="B431" t="s">
+        <v>139</v>
+      </c>
+      <c r="C431">
+        <v>2050</v>
+      </c>
+      <c r="D431" t="s">
+        <v>65</v>
+      </c>
+      <c r="E431">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A432" t="s">
+        <v>122</v>
+      </c>
+      <c r="B432" t="s">
+        <v>139</v>
+      </c>
+      <c r="C432">
+        <v>2050</v>
+      </c>
+      <c r="D432" t="s">
+        <v>66</v>
+      </c>
+      <c r="E432">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A433" t="s">
+        <v>122</v>
+      </c>
+      <c r="B433" t="s">
+        <v>139</v>
+      </c>
+      <c r="C433">
+        <v>2050</v>
+      </c>
+      <c r="D433" t="s">
+        <v>67</v>
+      </c>
+      <c r="E433">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A434" t="s">
+        <v>122</v>
+      </c>
+      <c r="B434" t="s">
+        <v>140</v>
+      </c>
+      <c r="C434">
+        <v>2030</v>
+      </c>
+      <c r="D434" t="s">
+        <v>65</v>
+      </c>
+      <c r="E434">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A435" t="s">
+        <v>122</v>
+      </c>
+      <c r="B435" t="s">
+        <v>140</v>
+      </c>
+      <c r="C435">
+        <v>2030</v>
+      </c>
+      <c r="D435" t="s">
+        <v>66</v>
+      </c>
+      <c r="E435">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A436" t="s">
+        <v>122</v>
+      </c>
+      <c r="B436" t="s">
+        <v>140</v>
+      </c>
+      <c r="C436">
+        <v>2030</v>
+      </c>
+      <c r="D436" t="s">
+        <v>67</v>
+      </c>
+      <c r="E436">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A437" t="s">
+        <v>122</v>
+      </c>
+      <c r="B437" t="s">
+        <v>140</v>
+      </c>
+      <c r="C437">
+        <v>2050</v>
+      </c>
+      <c r="D437" t="s">
+        <v>65</v>
+      </c>
+      <c r="E437">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A438" t="s">
+        <v>122</v>
+      </c>
+      <c r="B438" t="s">
+        <v>140</v>
+      </c>
+      <c r="C438">
+        <v>2050</v>
+      </c>
+      <c r="D438" t="s">
+        <v>66</v>
+      </c>
+      <c r="E438">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A439" t="s">
+        <v>122</v>
+      </c>
+      <c r="B439" t="s">
+        <v>140</v>
+      </c>
+      <c r="C439">
+        <v>2050</v>
+      </c>
+      <c r="D439" t="s">
+        <v>67</v>
+      </c>
+      <c r="E439">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A440" t="s">
+        <v>122</v>
+      </c>
+      <c r="B440" t="s">
+        <v>141</v>
+      </c>
+      <c r="C440">
+        <v>2030</v>
+      </c>
+      <c r="D440" t="s">
+        <v>65</v>
+      </c>
+      <c r="E440">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A441" t="s">
+        <v>122</v>
+      </c>
+      <c r="B441" t="s">
+        <v>141</v>
+      </c>
+      <c r="C441">
+        <v>2030</v>
+      </c>
+      <c r="D441" t="s">
+        <v>66</v>
+      </c>
+      <c r="E441">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A442" t="s">
+        <v>122</v>
+      </c>
+      <c r="B442" t="s">
+        <v>141</v>
+      </c>
+      <c r="C442">
+        <v>2030</v>
+      </c>
+      <c r="D442" t="s">
+        <v>67</v>
+      </c>
+      <c r="E442">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A443" t="s">
+        <v>122</v>
+      </c>
+      <c r="B443" t="s">
+        <v>141</v>
+      </c>
+      <c r="C443">
+        <v>2050</v>
+      </c>
+      <c r="D443" t="s">
+        <v>65</v>
+      </c>
+      <c r="E443">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A444" t="s">
+        <v>122</v>
+      </c>
+      <c r="B444" t="s">
+        <v>141</v>
+      </c>
+      <c r="C444">
+        <v>2050</v>
+      </c>
+      <c r="D444" t="s">
+        <v>66</v>
+      </c>
+      <c r="E444">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A445" t="s">
+        <v>122</v>
+      </c>
+      <c r="B445" t="s">
+        <v>141</v>
+      </c>
+      <c r="C445">
+        <v>2050</v>
+      </c>
+      <c r="D445" t="s">
+        <v>67</v>
+      </c>
+      <c r="E445">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A446" t="s">
+        <v>122</v>
+      </c>
+      <c r="B446" t="s">
+        <v>142</v>
+      </c>
+      <c r="C446">
+        <v>2030</v>
+      </c>
+      <c r="D446" t="s">
+        <v>65</v>
+      </c>
+      <c r="E446">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="447" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A447" t="s">
+        <v>122</v>
+      </c>
+      <c r="B447" t="s">
+        <v>142</v>
+      </c>
+      <c r="C447">
+        <v>2030</v>
+      </c>
+      <c r="D447" t="s">
+        <v>66</v>
+      </c>
+      <c r="E447">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A448" t="s">
+        <v>122</v>
+      </c>
+      <c r="B448" t="s">
+        <v>142</v>
+      </c>
+      <c r="C448">
+        <v>2030</v>
+      </c>
+      <c r="D448" t="s">
+        <v>67</v>
+      </c>
+      <c r="E448">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A449" t="s">
+        <v>122</v>
+      </c>
+      <c r="B449" t="s">
+        <v>142</v>
+      </c>
+      <c r="C449">
+        <v>2050</v>
+      </c>
+      <c r="D449" t="s">
+        <v>65</v>
+      </c>
+      <c r="E449">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="450" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A450" t="s">
+        <v>122</v>
+      </c>
+      <c r="B450" t="s">
+        <v>142</v>
+      </c>
+      <c r="C450">
+        <v>2050</v>
+      </c>
+      <c r="D450" t="s">
+        <v>66</v>
+      </c>
+      <c r="E450">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A451" t="s">
+        <v>122</v>
+      </c>
+      <c r="B451" t="s">
+        <v>142</v>
+      </c>
+      <c r="C451">
+        <v>2050</v>
+      </c>
+      <c r="D451" t="s">
+        <v>67</v>
+      </c>
+      <c r="E451">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A452" t="s">
+        <v>63</v>
+      </c>
+      <c r="B452" t="s">
+        <v>143</v>
+      </c>
+      <c r="C452">
+        <v>2030</v>
+      </c>
+      <c r="D452" t="s">
+        <v>65</v>
+      </c>
+      <c r="E452">
+        <v>0</v>
+      </c>
+      <c r="R452">
+        <v>3.1E-2</v>
+      </c>
+    </row>
+    <row r="453" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A453" t="s">
+        <v>63</v>
+      </c>
+      <c r="B453" t="s">
+        <v>143</v>
+      </c>
+      <c r="C453">
+        <v>2030</v>
+      </c>
+      <c r="D453" t="s">
+        <v>66</v>
+      </c>
+      <c r="E453">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="454" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A454" t="s">
+        <v>63</v>
+      </c>
+      <c r="B454" t="s">
+        <v>143</v>
+      </c>
+      <c r="C454">
+        <v>2030</v>
+      </c>
+      <c r="D454" t="s">
+        <v>67</v>
+      </c>
+      <c r="E454">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="455" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A455" t="s">
+        <v>63</v>
+      </c>
+      <c r="B455" t="s">
+        <v>143</v>
+      </c>
+      <c r="C455">
+        <v>2050</v>
+      </c>
+      <c r="D455" t="s">
+        <v>65</v>
+      </c>
+      <c r="E455">
+        <v>0</v>
+      </c>
+      <c r="R455">
+        <v>3.1E-2</v>
+      </c>
+    </row>
+    <row r="456" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A456" t="s">
+        <v>63</v>
+      </c>
+      <c r="B456" t="s">
+        <v>143</v>
+      </c>
+      <c r="C456">
+        <v>2050</v>
+      </c>
+      <c r="D456" t="s">
+        <v>66</v>
+      </c>
+      <c r="E456">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="457" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A457" t="s">
+        <v>63</v>
+      </c>
+      <c r="B457" t="s">
+        <v>143</v>
+      </c>
+      <c r="C457">
+        <v>2050</v>
+      </c>
+      <c r="D457" t="s">
+        <v>67</v>
+      </c>
+      <c r="E457">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="458" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A458" t="s">
+        <v>122</v>
+      </c>
+      <c r="B458" t="s">
+        <v>144</v>
+      </c>
+      <c r="C458">
+        <v>2030</v>
+      </c>
+      <c r="D458" t="s">
+        <v>65</v>
+      </c>
+      <c r="E458">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="459" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A459" t="s">
+        <v>122</v>
+      </c>
+      <c r="B459" t="s">
+        <v>144</v>
+      </c>
+      <c r="C459">
+        <v>2030</v>
+      </c>
+      <c r="D459" t="s">
+        <v>66</v>
+      </c>
+      <c r="E459">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A460" t="s">
+        <v>122</v>
+      </c>
+      <c r="B460" t="s">
+        <v>144</v>
+      </c>
+      <c r="C460">
+        <v>2030</v>
+      </c>
+      <c r="D460" t="s">
+        <v>67</v>
+      </c>
+      <c r="E460">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="461" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A461" t="s">
+        <v>122</v>
+      </c>
+      <c r="B461" t="s">
+        <v>144</v>
+      </c>
+      <c r="C461">
+        <v>2050</v>
+      </c>
+      <c r="D461" t="s">
+        <v>65</v>
+      </c>
+      <c r="E461">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="462" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A462" t="s">
+        <v>122</v>
+      </c>
+      <c r="B462" t="s">
+        <v>144</v>
+      </c>
+      <c r="C462">
+        <v>2050</v>
+      </c>
+      <c r="D462" t="s">
+        <v>66</v>
+      </c>
+      <c r="E462">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="463" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A463" t="s">
+        <v>122</v>
+      </c>
+      <c r="B463" t="s">
+        <v>144</v>
+      </c>
+      <c r="C463">
+        <v>2050</v>
+      </c>
+      <c r="D463" t="s">
+        <v>67</v>
+      </c>
+      <c r="E463">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="464" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A464" t="s">
+        <v>122</v>
+      </c>
+      <c r="B464" t="s">
+        <v>145</v>
+      </c>
+      <c r="C464">
+        <v>2030</v>
+      </c>
+      <c r="D464" t="s">
+        <v>65</v>
+      </c>
+      <c r="E464">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="465" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A465" t="s">
+        <v>122</v>
+      </c>
+      <c r="B465" t="s">
+        <v>145</v>
+      </c>
+      <c r="C465">
+        <v>2030</v>
+      </c>
+      <c r="D465" t="s">
+        <v>66</v>
+      </c>
+      <c r="E465">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A466" t="s">
+        <v>122</v>
+      </c>
+      <c r="B466" t="s">
+        <v>145</v>
+      </c>
+      <c r="C466">
+        <v>2030</v>
+      </c>
+      <c r="D466" t="s">
+        <v>67</v>
+      </c>
+      <c r="E466">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="467" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A467" t="s">
+        <v>122</v>
+      </c>
+      <c r="B467" t="s">
+        <v>145</v>
+      </c>
+      <c r="C467">
+        <v>2050</v>
+      </c>
+      <c r="D467" t="s">
+        <v>65</v>
+      </c>
+      <c r="E467">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A468" t="s">
+        <v>122</v>
+      </c>
+      <c r="B468" t="s">
+        <v>145</v>
+      </c>
+      <c r="C468">
+        <v>2050</v>
+      </c>
+      <c r="D468" t="s">
+        <v>66</v>
+      </c>
+      <c r="E468">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="469" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A469" t="s">
+        <v>122</v>
+      </c>
+      <c r="B469" t="s">
+        <v>145</v>
+      </c>
+      <c r="C469">
+        <v>2050</v>
+      </c>
+      <c r="D469" t="s">
+        <v>67</v>
+      </c>
+      <c r="E469">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="470" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A470" t="s">
+        <v>122</v>
+      </c>
+      <c r="B470" t="s">
+        <v>146</v>
+      </c>
+      <c r="C470">
+        <v>2030</v>
+      </c>
+      <c r="D470" t="s">
+        <v>65</v>
+      </c>
+      <c r="E470">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="471" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A471" t="s">
+        <v>122</v>
+      </c>
+      <c r="B471" t="s">
+        <v>146</v>
+      </c>
+      <c r="C471">
+        <v>2030</v>
+      </c>
+      <c r="D471" t="s">
+        <v>66</v>
+      </c>
+      <c r="E471">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="472" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A472" t="s">
+        <v>122</v>
+      </c>
+      <c r="B472" t="s">
+        <v>146</v>
+      </c>
+      <c r="C472">
+        <v>2030</v>
+      </c>
+      <c r="D472" t="s">
+        <v>67</v>
+      </c>
+      <c r="E472">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="473" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A473" t="s">
+        <v>122</v>
+      </c>
+      <c r="B473" t="s">
+        <v>146</v>
+      </c>
+      <c r="C473">
+        <v>2050</v>
+      </c>
+      <c r="D473" t="s">
+        <v>65</v>
+      </c>
+      <c r="E473">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="474" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A474" t="s">
+        <v>122</v>
+      </c>
+      <c r="B474" t="s">
+        <v>146</v>
+      </c>
+      <c r="C474">
+        <v>2050</v>
+      </c>
+      <c r="D474" t="s">
+        <v>66</v>
+      </c>
+      <c r="E474">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="475" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A475" t="s">
+        <v>122</v>
+      </c>
+      <c r="B475" t="s">
+        <v>146</v>
+      </c>
+      <c r="C475">
+        <v>2050</v>
+      </c>
+      <c r="D475" t="s">
+        <v>67</v>
+      </c>
+      <c r="E475">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="476" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A476" t="s">
+        <v>122</v>
+      </c>
+      <c r="B476" t="s">
+        <v>147</v>
+      </c>
+      <c r="C476">
+        <v>2030</v>
+      </c>
+      <c r="D476" t="s">
+        <v>65</v>
+      </c>
+      <c r="E476">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="477" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A477" t="s">
+        <v>122</v>
+      </c>
+      <c r="B477" t="s">
+        <v>147</v>
+      </c>
+      <c r="C477">
+        <v>2030</v>
+      </c>
+      <c r="D477" t="s">
+        <v>66</v>
+      </c>
+      <c r="E477">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="478" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A478" t="s">
+        <v>122</v>
+      </c>
+      <c r="B478" t="s">
+        <v>147</v>
+      </c>
+      <c r="C478">
+        <v>2030</v>
+      </c>
+      <c r="D478" t="s">
+        <v>67</v>
+      </c>
+      <c r="E478">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="479" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A479" t="s">
+        <v>122</v>
+      </c>
+      <c r="B479" t="s">
+        <v>147</v>
+      </c>
+      <c r="C479">
+        <v>2050</v>
+      </c>
+      <c r="D479" t="s">
+        <v>65</v>
+      </c>
+      <c r="E479">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A480" t="s">
+        <v>122</v>
+      </c>
+      <c r="B480" t="s">
+        <v>147</v>
+      </c>
+      <c r="C480">
+        <v>2050</v>
+      </c>
+      <c r="D480" t="s">
+        <v>66</v>
+      </c>
+      <c r="E480">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="481" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A481" t="s">
+        <v>122</v>
+      </c>
+      <c r="B481" t="s">
+        <v>147</v>
+      </c>
+      <c r="C481">
+        <v>2050</v>
+      </c>
+      <c r="D481" t="s">
+        <v>67</v>
+      </c>
+      <c r="E481">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="482" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A482" t="s">
+        <v>122</v>
+      </c>
+      <c r="B482" t="s">
+        <v>148</v>
+      </c>
+      <c r="C482">
+        <v>2030</v>
+      </c>
+      <c r="D482" t="s">
+        <v>65</v>
+      </c>
+      <c r="E482">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="483" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A483" t="s">
+        <v>122</v>
+      </c>
+      <c r="B483" t="s">
+        <v>148</v>
+      </c>
+      <c r="C483">
+        <v>2030</v>
+      </c>
+      <c r="D483" t="s">
+        <v>66</v>
+      </c>
+      <c r="E483">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="484" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A484" t="s">
+        <v>122</v>
+      </c>
+      <c r="B484" t="s">
+        <v>148</v>
+      </c>
+      <c r="C484">
+        <v>2030</v>
+      </c>
+      <c r="D484" t="s">
+        <v>67</v>
+      </c>
+      <c r="E484">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="485" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A485" t="s">
+        <v>122</v>
+      </c>
+      <c r="B485" t="s">
+        <v>148</v>
+      </c>
+      <c r="C485">
+        <v>2050</v>
+      </c>
+      <c r="D485" t="s">
+        <v>65</v>
+      </c>
+      <c r="E485">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="486" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A486" t="s">
+        <v>122</v>
+      </c>
+      <c r="B486" t="s">
+        <v>148</v>
+      </c>
+      <c r="C486">
+        <v>2050</v>
+      </c>
+      <c r="D486" t="s">
+        <v>66</v>
+      </c>
+      <c r="E486">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="487" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A487" t="s">
+        <v>122</v>
+      </c>
+      <c r="B487" t="s">
+        <v>148</v>
+      </c>
+      <c r="C487">
+        <v>2050</v>
+      </c>
+      <c r="D487" t="s">
+        <v>67</v>
+      </c>
+      <c r="E487">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="488" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A488" t="s">
+        <v>122</v>
+      </c>
+      <c r="B488" t="s">
+        <v>149</v>
+      </c>
+      <c r="C488">
+        <v>2030</v>
+      </c>
+      <c r="D488" t="s">
+        <v>65</v>
+      </c>
+      <c r="E488">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="489" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A489" t="s">
+        <v>122</v>
+      </c>
+      <c r="B489" t="s">
+        <v>149</v>
+      </c>
+      <c r="C489">
+        <v>2030</v>
+      </c>
+      <c r="D489" t="s">
+        <v>66</v>
+      </c>
+      <c r="E489">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="490" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A490" t="s">
+        <v>122</v>
+      </c>
+      <c r="B490" t="s">
+        <v>149</v>
+      </c>
+      <c r="C490">
+        <v>2030</v>
+      </c>
+      <c r="D490" t="s">
+        <v>67</v>
+      </c>
+      <c r="E490">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="491" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A491" t="s">
+        <v>122</v>
+      </c>
+      <c r="B491" t="s">
+        <v>149</v>
+      </c>
+      <c r="C491">
+        <v>2050</v>
+      </c>
+      <c r="D491" t="s">
+        <v>65</v>
+      </c>
+      <c r="E491">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="492" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A492" t="s">
+        <v>122</v>
+      </c>
+      <c r="B492" t="s">
+        <v>149</v>
+      </c>
+      <c r="C492">
+        <v>2050</v>
+      </c>
+      <c r="D492" t="s">
+        <v>66</v>
+      </c>
+      <c r="E492">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="493" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A493" t="s">
+        <v>122</v>
+      </c>
+      <c r="B493" t="s">
+        <v>149</v>
+      </c>
+      <c r="C493">
+        <v>2050</v>
+      </c>
+      <c r="D493" t="s">
+        <v>67</v>
+      </c>
+      <c r="E493">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="494" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A494" t="s">
+        <v>122</v>
+      </c>
+      <c r="B494" t="s">
+        <v>150</v>
+      </c>
+      <c r="C494">
+        <v>2030</v>
+      </c>
+      <c r="D494" t="s">
+        <v>65</v>
+      </c>
+      <c r="E494">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="495" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A495" t="s">
+        <v>122</v>
+      </c>
+      <c r="B495" t="s">
+        <v>150</v>
+      </c>
+      <c r="C495">
+        <v>2030</v>
+      </c>
+      <c r="D495" t="s">
+        <v>66</v>
+      </c>
+      <c r="E495">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="496" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A496" t="s">
+        <v>122</v>
+      </c>
+      <c r="B496" t="s">
+        <v>150</v>
+      </c>
+      <c r="C496">
+        <v>2030</v>
+      </c>
+      <c r="D496" t="s">
+        <v>67</v>
+      </c>
+      <c r="E496">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="497" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A497" t="s">
+        <v>122</v>
+      </c>
+      <c r="B497" t="s">
+        <v>150</v>
+      </c>
+      <c r="C497">
+        <v>2050</v>
+      </c>
+      <c r="D497" t="s">
+        <v>65</v>
+      </c>
+      <c r="E497">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="498" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A498" t="s">
+        <v>122</v>
+      </c>
+      <c r="B498" t="s">
+        <v>150</v>
+      </c>
+      <c r="C498">
+        <v>2050</v>
+      </c>
+      <c r="D498" t="s">
+        <v>66</v>
+      </c>
+      <c r="E498">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="499" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A499" t="s">
+        <v>122</v>
+      </c>
+      <c r="B499" t="s">
+        <v>150</v>
+      </c>
+      <c r="C499">
+        <v>2050</v>
+      </c>
+      <c r="D499" t="s">
+        <v>67</v>
+      </c>
+      <c r="E499">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="500" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A500" t="s">
+        <v>122</v>
+      </c>
+      <c r="B500" t="s">
+        <v>151</v>
+      </c>
+      <c r="C500">
+        <v>2030</v>
+      </c>
+      <c r="D500" t="s">
+        <v>65</v>
+      </c>
+      <c r="E500">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="501" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A501" t="s">
+        <v>122</v>
+      </c>
+      <c r="B501" t="s">
+        <v>151</v>
+      </c>
+      <c r="C501">
+        <v>2030</v>
+      </c>
+      <c r="D501" t="s">
+        <v>66</v>
+      </c>
+      <c r="E501">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="502" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A502" t="s">
+        <v>122</v>
+      </c>
+      <c r="B502" t="s">
+        <v>151</v>
+      </c>
+      <c r="C502">
+        <v>2030</v>
+      </c>
+      <c r="D502" t="s">
+        <v>67</v>
+      </c>
+      <c r="E502">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="503" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A503" t="s">
+        <v>122</v>
+      </c>
+      <c r="B503" t="s">
+        <v>151</v>
+      </c>
+      <c r="C503">
+        <v>2050</v>
+      </c>
+      <c r="D503" t="s">
+        <v>65</v>
+      </c>
+      <c r="E503">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="504" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A504" t="s">
+        <v>122</v>
+      </c>
+      <c r="B504" t="s">
+        <v>151</v>
+      </c>
+      <c r="C504">
+        <v>2050</v>
+      </c>
+      <c r="D504" t="s">
+        <v>66</v>
+      </c>
+      <c r="E504">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="505" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A505" t="s">
+        <v>122</v>
+      </c>
+      <c r="B505" t="s">
+        <v>151</v>
+      </c>
+      <c r="C505">
+        <v>2050</v>
+      </c>
+      <c r="D505" t="s">
+        <v>67</v>
+      </c>
+      <c r="E505">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="506" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A506" t="s">
+        <v>122</v>
+      </c>
+      <c r="B506" t="s">
+        <v>152</v>
+      </c>
+      <c r="C506">
+        <v>2030</v>
+      </c>
+      <c r="D506" t="s">
+        <v>65</v>
+      </c>
+      <c r="E506">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="507" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A507" t="s">
+        <v>122</v>
+      </c>
+      <c r="B507" t="s">
+        <v>152</v>
+      </c>
+      <c r="C507">
+        <v>2030</v>
+      </c>
+      <c r="D507" t="s">
+        <v>66</v>
+      </c>
+      <c r="E507">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="508" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A508" t="s">
+        <v>122</v>
+      </c>
+      <c r="B508" t="s">
+        <v>152</v>
+      </c>
+      <c r="C508">
+        <v>2030</v>
+      </c>
+      <c r="D508" t="s">
+        <v>67</v>
+      </c>
+      <c r="E508">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="509" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A509" t="s">
+        <v>122</v>
+      </c>
+      <c r="B509" t="s">
+        <v>152</v>
+      </c>
+      <c r="C509">
+        <v>2050</v>
+      </c>
+      <c r="D509" t="s">
+        <v>65</v>
+      </c>
+      <c r="E509">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="510" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A510" t="s">
+        <v>122</v>
+      </c>
+      <c r="B510" t="s">
+        <v>152</v>
+      </c>
+      <c r="C510">
+        <v>2050</v>
+      </c>
+      <c r="D510" t="s">
+        <v>66</v>
+      </c>
+      <c r="E510">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="511" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A511" t="s">
+        <v>122</v>
+      </c>
+      <c r="B511" t="s">
+        <v>152</v>
+      </c>
+      <c r="C511">
+        <v>2050</v>
+      </c>
+      <c r="D511" t="s">
+        <v>67</v>
+      </c>
+      <c r="E511">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="512" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A512" t="s">
+        <v>63</v>
+      </c>
+      <c r="B512" t="s">
+        <v>153</v>
+      </c>
+      <c r="C512">
+        <v>2030</v>
+      </c>
+      <c r="D512" t="s">
+        <v>65</v>
+      </c>
+      <c r="E512">
+        <v>0</v>
+      </c>
+      <c r="R512">
+        <v>2.0999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="513" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A513" t="s">
+        <v>63</v>
+      </c>
+      <c r="B513" t="s">
+        <v>153</v>
+      </c>
+      <c r="C513">
+        <v>2030</v>
+      </c>
+      <c r="D513" t="s">
+        <v>66</v>
+      </c>
+      <c r="E513">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="514" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A514" t="s">
+        <v>63</v>
+      </c>
+      <c r="B514" t="s">
+        <v>153</v>
+      </c>
+      <c r="C514">
+        <v>2030</v>
+      </c>
+      <c r="D514" t="s">
+        <v>67</v>
+      </c>
+      <c r="E514">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="515" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A515" t="s">
+        <v>63</v>
+      </c>
+      <c r="B515" t="s">
+        <v>153</v>
+      </c>
+      <c r="C515">
+        <v>2050</v>
+      </c>
+      <c r="D515" t="s">
+        <v>65</v>
+      </c>
+      <c r="E515">
+        <v>0</v>
+      </c>
+      <c r="R515">
+        <v>2.0999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="516" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A516" t="s">
+        <v>63</v>
+      </c>
+      <c r="B516" t="s">
+        <v>153</v>
+      </c>
+      <c r="C516">
+        <v>2050</v>
+      </c>
+      <c r="D516" t="s">
+        <v>66</v>
+      </c>
+      <c r="E516">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="517" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A517" t="s">
+        <v>63</v>
+      </c>
+      <c r="B517" t="s">
+        <v>153</v>
+      </c>
+      <c r="C517">
+        <v>2050</v>
+      </c>
+      <c r="D517" t="s">
+        <v>67</v>
+      </c>
+      <c r="E517">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="518" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A518" t="s">
+        <v>122</v>
+      </c>
+      <c r="B518" t="s">
+        <v>154</v>
+      </c>
+      <c r="C518">
+        <v>2030</v>
+      </c>
+      <c r="D518" t="s">
+        <v>65</v>
+      </c>
+      <c r="E518">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="519" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A519" t="s">
+        <v>122</v>
+      </c>
+      <c r="B519" t="s">
+        <v>154</v>
+      </c>
+      <c r="C519">
+        <v>2030</v>
+      </c>
+      <c r="D519" t="s">
+        <v>66</v>
+      </c>
+      <c r="E519">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="520" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A520" t="s">
+        <v>122</v>
+      </c>
+      <c r="B520" t="s">
+        <v>154</v>
+      </c>
+      <c r="C520">
+        <v>2030</v>
+      </c>
+      <c r="D520" t="s">
+        <v>67</v>
+      </c>
+      <c r="E520">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="521" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A521" t="s">
+        <v>122</v>
+      </c>
+      <c r="B521" t="s">
+        <v>154</v>
+      </c>
+      <c r="C521">
+        <v>2050</v>
+      </c>
+      <c r="D521" t="s">
+        <v>65</v>
+      </c>
+      <c r="E521">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="522" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A522" t="s">
+        <v>122</v>
+      </c>
+      <c r="B522" t="s">
+        <v>154</v>
+      </c>
+      <c r="C522">
+        <v>2050</v>
+      </c>
+      <c r="D522" t="s">
+        <v>66</v>
+      </c>
+      <c r="E522">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="523" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A523" t="s">
+        <v>122</v>
+      </c>
+      <c r="B523" t="s">
+        <v>154</v>
+      </c>
+      <c r="C523">
+        <v>2050</v>
+      </c>
+      <c r="D523" t="s">
+        <v>67</v>
+      </c>
+      <c r="E523">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="524" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A524" t="s">
+        <v>122</v>
+      </c>
+      <c r="B524" t="s">
+        <v>155</v>
+      </c>
+      <c r="C524">
+        <v>2030</v>
+      </c>
+      <c r="D524" t="s">
+        <v>65</v>
+      </c>
+      <c r="E524">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="525" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A525" t="s">
+        <v>122</v>
+      </c>
+      <c r="B525" t="s">
+        <v>155</v>
+      </c>
+      <c r="C525">
+        <v>2030</v>
+      </c>
+      <c r="D525" t="s">
+        <v>66</v>
+      </c>
+      <c r="E525">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="526" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A526" t="s">
+        <v>122</v>
+      </c>
+      <c r="B526" t="s">
+        <v>155</v>
+      </c>
+      <c r="C526">
+        <v>2030</v>
+      </c>
+      <c r="D526" t="s">
+        <v>67</v>
+      </c>
+      <c r="E526">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="527" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A527" t="s">
+        <v>122</v>
+      </c>
+      <c r="B527" t="s">
+        <v>155</v>
+      </c>
+      <c r="C527">
+        <v>2050</v>
+      </c>
+      <c r="D527" t="s">
+        <v>65</v>
+      </c>
+      <c r="E527">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="528" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A528" t="s">
+        <v>122</v>
+      </c>
+      <c r="B528" t="s">
+        <v>155</v>
+      </c>
+      <c r="C528">
+        <v>2050</v>
+      </c>
+      <c r="D528" t="s">
+        <v>66</v>
+      </c>
+      <c r="E528">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="529" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A529" t="s">
+        <v>122</v>
+      </c>
+      <c r="B529" t="s">
+        <v>155</v>
+      </c>
+      <c r="C529">
+        <v>2050</v>
+      </c>
+      <c r="D529" t="s">
+        <v>67</v>
+      </c>
+      <c r="E529">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="530" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A530" t="s">
+        <v>122</v>
+      </c>
+      <c r="B530" t="s">
+        <v>156</v>
+      </c>
+      <c r="C530">
+        <v>2030</v>
+      </c>
+      <c r="D530" t="s">
+        <v>65</v>
+      </c>
+      <c r="E530">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="531" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A531" t="s">
+        <v>122</v>
+      </c>
+      <c r="B531" t="s">
+        <v>156</v>
+      </c>
+      <c r="C531">
+        <v>2030</v>
+      </c>
+      <c r="D531" t="s">
+        <v>66</v>
+      </c>
+      <c r="E531">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="532" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A532" t="s">
+        <v>122</v>
+      </c>
+      <c r="B532" t="s">
+        <v>156</v>
+      </c>
+      <c r="C532">
+        <v>2030</v>
+      </c>
+      <c r="D532" t="s">
+        <v>67</v>
+      </c>
+      <c r="E532">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="533" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A533" t="s">
+        <v>122</v>
+      </c>
+      <c r="B533" t="s">
+        <v>156</v>
+      </c>
+      <c r="C533">
+        <v>2050</v>
+      </c>
+      <c r="D533" t="s">
+        <v>65</v>
+      </c>
+      <c r="E533">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="534" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A534" t="s">
+        <v>122</v>
+      </c>
+      <c r="B534" t="s">
+        <v>156</v>
+      </c>
+      <c r="C534">
+        <v>2050</v>
+      </c>
+      <c r="D534" t="s">
+        <v>66</v>
+      </c>
+      <c r="E534">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="535" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A535" t="s">
+        <v>122</v>
+      </c>
+      <c r="B535" t="s">
+        <v>156</v>
+      </c>
+      <c r="C535">
+        <v>2050</v>
+      </c>
+      <c r="D535" t="s">
+        <v>67</v>
+      </c>
+      <c r="E535">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="536" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A536" t="s">
+        <v>122</v>
+      </c>
+      <c r="B536" t="s">
+        <v>157</v>
+      </c>
+      <c r="C536">
+        <v>2030</v>
+      </c>
+      <c r="D536" t="s">
+        <v>65</v>
+      </c>
+      <c r="E536">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="537" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A537" t="s">
+        <v>122</v>
+      </c>
+      <c r="B537" t="s">
+        <v>157</v>
+      </c>
+      <c r="C537">
+        <v>2030</v>
+      </c>
+      <c r="D537" t="s">
+        <v>66</v>
+      </c>
+      <c r="E537">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="538" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A538" t="s">
+        <v>122</v>
+      </c>
+      <c r="B538" t="s">
+        <v>157</v>
+      </c>
+      <c r="C538">
+        <v>2030</v>
+      </c>
+      <c r="D538" t="s">
+        <v>67</v>
+      </c>
+      <c r="E538">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="539" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A539" t="s">
+        <v>122</v>
+      </c>
+      <c r="B539" t="s">
+        <v>157</v>
+      </c>
+      <c r="C539">
+        <v>2050</v>
+      </c>
+      <c r="D539" t="s">
+        <v>65</v>
+      </c>
+      <c r="E539">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="540" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A540" t="s">
+        <v>122</v>
+      </c>
+      <c r="B540" t="s">
+        <v>157</v>
+      </c>
+      <c r="C540">
+        <v>2050</v>
+      </c>
+      <c r="D540" t="s">
+        <v>66</v>
+      </c>
+      <c r="E540">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="541" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A541" t="s">
+        <v>122</v>
+      </c>
+      <c r="B541" t="s">
+        <v>157</v>
+      </c>
+      <c r="C541">
+        <v>2050</v>
+      </c>
+      <c r="D541" t="s">
+        <v>67</v>
+      </c>
+      <c r="E541">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="542" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A542" t="s">
+        <v>122</v>
+      </c>
+      <c r="B542" t="s">
+        <v>158</v>
+      </c>
+      <c r="C542">
+        <v>2030</v>
+      </c>
+      <c r="D542" t="s">
+        <v>65</v>
+      </c>
+      <c r="E542">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="543" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A543" t="s">
+        <v>122</v>
+      </c>
+      <c r="B543" t="s">
+        <v>158</v>
+      </c>
+      <c r="C543">
+        <v>2030</v>
+      </c>
+      <c r="D543" t="s">
+        <v>66</v>
+      </c>
+      <c r="E543">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="544" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A544" t="s">
+        <v>122</v>
+      </c>
+      <c r="B544" t="s">
+        <v>158</v>
+      </c>
+      <c r="C544">
+        <v>2030</v>
+      </c>
+      <c r="D544" t="s">
+        <v>67</v>
+      </c>
+      <c r="E544">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="545" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A545" t="s">
+        <v>122</v>
+      </c>
+      <c r="B545" t="s">
+        <v>158</v>
+      </c>
+      <c r="C545">
+        <v>2050</v>
+      </c>
+      <c r="D545" t="s">
+        <v>65</v>
+      </c>
+      <c r="E545">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="546" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A546" t="s">
+        <v>122</v>
+      </c>
+      <c r="B546" t="s">
+        <v>158</v>
+      </c>
+      <c r="C546">
+        <v>2050</v>
+      </c>
+      <c r="D546" t="s">
+        <v>66</v>
+      </c>
+      <c r="E546">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="547" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A547" t="s">
+        <v>122</v>
+      </c>
+      <c r="B547" t="s">
+        <v>158</v>
+      </c>
+      <c r="C547">
+        <v>2050</v>
+      </c>
+      <c r="D547" t="s">
+        <v>67</v>
+      </c>
+      <c r="E547">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="548" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A548" t="s">
+        <v>122</v>
+      </c>
+      <c r="B548" t="s">
+        <v>159</v>
+      </c>
+      <c r="C548">
+        <v>2030</v>
+      </c>
+      <c r="D548" t="s">
+        <v>65</v>
+      </c>
+      <c r="E548">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="549" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A549" t="s">
+        <v>122</v>
+      </c>
+      <c r="B549" t="s">
+        <v>159</v>
+      </c>
+      <c r="C549">
+        <v>2030</v>
+      </c>
+      <c r="D549" t="s">
+        <v>66</v>
+      </c>
+      <c r="E549">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="550" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A550" t="s">
+        <v>122</v>
+      </c>
+      <c r="B550" t="s">
+        <v>159</v>
+      </c>
+      <c r="C550">
+        <v>2030</v>
+      </c>
+      <c r="D550" t="s">
+        <v>67</v>
+      </c>
+      <c r="E550">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="551" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A551" t="s">
+        <v>122</v>
+      </c>
+      <c r="B551" t="s">
+        <v>159</v>
+      </c>
+      <c r="C551">
+        <v>2050</v>
+      </c>
+      <c r="D551" t="s">
+        <v>65</v>
+      </c>
+      <c r="E551">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="552" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A552" t="s">
+        <v>122</v>
+      </c>
+      <c r="B552" t="s">
+        <v>159</v>
+      </c>
+      <c r="C552">
+        <v>2050</v>
+      </c>
+      <c r="D552" t="s">
+        <v>66</v>
+      </c>
+      <c r="E552">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="553" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A553" t="s">
+        <v>122</v>
+      </c>
+      <c r="B553" t="s">
+        <v>159</v>
+      </c>
+      <c r="C553">
+        <v>2050</v>
+      </c>
+      <c r="D553" t="s">
+        <v>67</v>
+      </c>
+      <c r="E553">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="554" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A554" t="s">
+        <v>122</v>
+      </c>
+      <c r="B554" t="s">
+        <v>160</v>
+      </c>
+      <c r="C554">
+        <v>2030</v>
+      </c>
+      <c r="D554" t="s">
+        <v>65</v>
+      </c>
+      <c r="E554">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="555" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A555" t="s">
+        <v>122</v>
+      </c>
+      <c r="B555" t="s">
+        <v>160</v>
+      </c>
+      <c r="C555">
+        <v>2030</v>
+      </c>
+      <c r="D555" t="s">
+        <v>66</v>
+      </c>
+      <c r="E555">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="556" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A556" t="s">
+        <v>122</v>
+      </c>
+      <c r="B556" t="s">
+        <v>160</v>
+      </c>
+      <c r="C556">
+        <v>2030</v>
+      </c>
+      <c r="D556" t="s">
+        <v>67</v>
+      </c>
+      <c r="E556">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="557" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A557" t="s">
+        <v>122</v>
+      </c>
+      <c r="B557" t="s">
+        <v>160</v>
+      </c>
+      <c r="C557">
+        <v>2050</v>
+      </c>
+      <c r="D557" t="s">
+        <v>65</v>
+      </c>
+      <c r="E557">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="558" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A558" t="s">
+        <v>122</v>
+      </c>
+      <c r="B558" t="s">
+        <v>160</v>
+      </c>
+      <c r="C558">
+        <v>2050</v>
+      </c>
+      <c r="D558" t="s">
+        <v>66</v>
+      </c>
+      <c r="E558">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="559" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A559" t="s">
+        <v>122</v>
+      </c>
+      <c r="B559" t="s">
+        <v>160</v>
+      </c>
+      <c r="C559">
+        <v>2050</v>
+      </c>
+      <c r="D559" t="s">
+        <v>67</v>
+      </c>
+      <c r="E559">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="560" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A560" t="s">
+        <v>122</v>
+      </c>
+      <c r="B560" t="s">
+        <v>161</v>
+      </c>
+      <c r="C560">
+        <v>2030</v>
+      </c>
+      <c r="D560" t="s">
+        <v>65</v>
+      </c>
+      <c r="E560">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="561" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A561" t="s">
+        <v>122</v>
+      </c>
+      <c r="B561" t="s">
+        <v>161</v>
+      </c>
+      <c r="C561">
+        <v>2030</v>
+      </c>
+      <c r="D561" t="s">
+        <v>66</v>
+      </c>
+      <c r="E561">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="562" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A562" t="s">
+        <v>122</v>
+      </c>
+      <c r="B562" t="s">
+        <v>161</v>
+      </c>
+      <c r="C562">
+        <v>2030</v>
+      </c>
+      <c r="D562" t="s">
+        <v>67</v>
+      </c>
+      <c r="E562">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="563" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A563" t="s">
+        <v>122</v>
+      </c>
+      <c r="B563" t="s">
+        <v>161</v>
+      </c>
+      <c r="C563">
+        <v>2050</v>
+      </c>
+      <c r="D563" t="s">
+        <v>65</v>
+      </c>
+      <c r="E563">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="564" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A564" t="s">
+        <v>122</v>
+      </c>
+      <c r="B564" t="s">
+        <v>161</v>
+      </c>
+      <c r="C564">
+        <v>2050</v>
+      </c>
+      <c r="D564" t="s">
+        <v>66</v>
+      </c>
+      <c r="E564">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="565" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A565" t="s">
+        <v>122</v>
+      </c>
+      <c r="B565" t="s">
+        <v>161</v>
+      </c>
+      <c r="C565">
+        <v>2050</v>
+      </c>
+      <c r="D565" t="s">
+        <v>67</v>
+      </c>
+      <c r="E565">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="566" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A566" t="s">
+        <v>122</v>
+      </c>
+      <c r="B566" t="s">
+        <v>162</v>
+      </c>
+      <c r="C566">
+        <v>2030</v>
+      </c>
+      <c r="D566" t="s">
+        <v>65</v>
+      </c>
+      <c r="E566">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="567" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A567" t="s">
+        <v>122</v>
+      </c>
+      <c r="B567" t="s">
+        <v>162</v>
+      </c>
+      <c r="C567">
+        <v>2030</v>
+      </c>
+      <c r="D567" t="s">
+        <v>66</v>
+      </c>
+      <c r="E567">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="568" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A568" t="s">
+        <v>122</v>
+      </c>
+      <c r="B568" t="s">
+        <v>162</v>
+      </c>
+      <c r="C568">
+        <v>2030</v>
+      </c>
+      <c r="D568" t="s">
+        <v>67</v>
+      </c>
+      <c r="E568">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="569" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A569" t="s">
+        <v>122</v>
+      </c>
+      <c r="B569" t="s">
+        <v>162</v>
+      </c>
+      <c r="C569">
+        <v>2050</v>
+      </c>
+      <c r="D569" t="s">
+        <v>65</v>
+      </c>
+      <c r="E569">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="570" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A570" t="s">
+        <v>122</v>
+      </c>
+      <c r="B570" t="s">
+        <v>162</v>
+      </c>
+      <c r="C570">
+        <v>2050</v>
+      </c>
+      <c r="D570" t="s">
+        <v>66</v>
+      </c>
+      <c r="E570">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="571" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A571" t="s">
+        <v>122</v>
+      </c>
+      <c r="B571" t="s">
+        <v>162</v>
+      </c>
+      <c r="C571">
+        <v>2050</v>
+      </c>
+      <c r="D571" t="s">
+        <v>67</v>
+      </c>
+      <c r="E571">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="572" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A572" t="s">
+        <v>63</v>
+      </c>
+      <c r="B572" t="s">
+        <v>163</v>
+      </c>
+      <c r="C572">
+        <v>2030</v>
+      </c>
+      <c r="D572" t="s">
+        <v>65</v>
+      </c>
+      <c r="E572">
+        <v>0</v>
+      </c>
+      <c r="R572">
+        <v>-1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="573" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A573" t="s">
+        <v>63</v>
+      </c>
+      <c r="B573" t="s">
+        <v>163</v>
+      </c>
+      <c r="C573">
+        <v>2030</v>
+      </c>
+      <c r="D573" t="s">
+        <v>66</v>
+      </c>
+      <c r="E573">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="574" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A574" t="s">
+        <v>63</v>
+      </c>
+      <c r="B574" t="s">
+        <v>163</v>
+      </c>
+      <c r="C574">
+        <v>2030</v>
+      </c>
+      <c r="D574" t="s">
+        <v>67</v>
+      </c>
+      <c r="E574">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="575" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A575" t="s">
+        <v>63</v>
+      </c>
+      <c r="B575" t="s">
+        <v>163</v>
+      </c>
+      <c r="C575">
+        <v>2050</v>
+      </c>
+      <c r="D575" t="s">
+        <v>65</v>
+      </c>
+      <c r="E575">
+        <v>0</v>
+      </c>
+      <c r="R575">
+        <v>-1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="576" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A576" t="s">
+        <v>63</v>
+      </c>
+      <c r="B576" t="s">
+        <v>163</v>
+      </c>
+      <c r="C576">
+        <v>2050</v>
+      </c>
+      <c r="D576" t="s">
+        <v>66</v>
+      </c>
+      <c r="E576">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="577" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A577" t="s">
+        <v>63</v>
+      </c>
+      <c r="B577" t="s">
+        <v>163</v>
+      </c>
+      <c r="C577">
+        <v>2050</v>
+      </c>
+      <c r="D577" t="s">
+        <v>67</v>
+      </c>
+      <c r="E577">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="578" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A578" t="s">
+        <v>122</v>
+      </c>
+      <c r="B578" t="s">
+        <v>164</v>
+      </c>
+      <c r="C578">
+        <v>2030</v>
+      </c>
+      <c r="D578" t="s">
+        <v>65</v>
+      </c>
+      <c r="E578">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="579" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A579" t="s">
+        <v>122</v>
+      </c>
+      <c r="B579" t="s">
+        <v>164</v>
+      </c>
+      <c r="C579">
+        <v>2030</v>
+      </c>
+      <c r="D579" t="s">
+        <v>66</v>
+      </c>
+      <c r="E579">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="580" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A580" t="s">
+        <v>122</v>
+      </c>
+      <c r="B580" t="s">
+        <v>164</v>
+      </c>
+      <c r="C580">
+        <v>2030</v>
+      </c>
+      <c r="D580" t="s">
+        <v>67</v>
+      </c>
+      <c r="E580">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="581" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A581" t="s">
+        <v>122</v>
+      </c>
+      <c r="B581" t="s">
+        <v>164</v>
+      </c>
+      <c r="C581">
+        <v>2050</v>
+      </c>
+      <c r="D581" t="s">
+        <v>65</v>
+      </c>
+      <c r="E581">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="582" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A582" t="s">
+        <v>122</v>
+      </c>
+      <c r="B582" t="s">
+        <v>164</v>
+      </c>
+      <c r="C582">
+        <v>2050</v>
+      </c>
+      <c r="D582" t="s">
+        <v>66</v>
+      </c>
+      <c r="E582">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="583" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A583" t="s">
+        <v>122</v>
+      </c>
+      <c r="B583" t="s">
+        <v>164</v>
+      </c>
+      <c r="C583">
+        <v>2050</v>
+      </c>
+      <c r="D583" t="s">
+        <v>67</v>
+      </c>
+      <c r="E583">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="584" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A584" t="s">
+        <v>122</v>
+      </c>
+      <c r="B584" t="s">
+        <v>165</v>
+      </c>
+      <c r="C584">
+        <v>2030</v>
+      </c>
+      <c r="D584" t="s">
+        <v>65</v>
+      </c>
+      <c r="E584">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="585" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A585" t="s">
+        <v>122</v>
+      </c>
+      <c r="B585" t="s">
+        <v>165</v>
+      </c>
+      <c r="C585">
+        <v>2030</v>
+      </c>
+      <c r="D585" t="s">
+        <v>66</v>
+      </c>
+      <c r="E585">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="586" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A586" t="s">
+        <v>122</v>
+      </c>
+      <c r="B586" t="s">
+        <v>165</v>
+      </c>
+      <c r="C586">
+        <v>2030</v>
+      </c>
+      <c r="D586" t="s">
+        <v>67</v>
+      </c>
+      <c r="E586">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="587" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A587" t="s">
+        <v>122</v>
+      </c>
+      <c r="B587" t="s">
+        <v>165</v>
+      </c>
+      <c r="C587">
+        <v>2050</v>
+      </c>
+      <c r="D587" t="s">
+        <v>65</v>
+      </c>
+      <c r="E587">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="588" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A588" t="s">
+        <v>122</v>
+      </c>
+      <c r="B588" t="s">
+        <v>165</v>
+      </c>
+      <c r="C588">
+        <v>2050</v>
+      </c>
+      <c r="D588" t="s">
+        <v>66</v>
+      </c>
+      <c r="E588">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="589" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A589" t="s">
+        <v>122</v>
+      </c>
+      <c r="B589" t="s">
+        <v>165</v>
+      </c>
+      <c r="C589">
+        <v>2050</v>
+      </c>
+      <c r="D589" t="s">
+        <v>67</v>
+      </c>
+      <c r="E589">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="590" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A590" t="s">
+        <v>122</v>
+      </c>
+      <c r="B590" t="s">
+        <v>166</v>
+      </c>
+      <c r="C590">
+        <v>2030</v>
+      </c>
+      <c r="D590" t="s">
+        <v>65</v>
+      </c>
+      <c r="E590">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="591" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A591" t="s">
+        <v>122</v>
+      </c>
+      <c r="B591" t="s">
+        <v>166</v>
+      </c>
+      <c r="C591">
+        <v>2030</v>
+      </c>
+      <c r="D591" t="s">
+        <v>66</v>
+      </c>
+      <c r="E591">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="592" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A592" t="s">
+        <v>122</v>
+      </c>
+      <c r="B592" t="s">
+        <v>166</v>
+      </c>
+      <c r="C592">
+        <v>2030</v>
+      </c>
+      <c r="D592" t="s">
+        <v>67</v>
+      </c>
+      <c r="E592">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="593" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A593" t="s">
+        <v>122</v>
+      </c>
+      <c r="B593" t="s">
+        <v>166</v>
+      </c>
+      <c r="C593">
+        <v>2050</v>
+      </c>
+      <c r="D593" t="s">
+        <v>65</v>
+      </c>
+      <c r="E593">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="594" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A594" t="s">
+        <v>122</v>
+      </c>
+      <c r="B594" t="s">
+        <v>166</v>
+      </c>
+      <c r="C594">
+        <v>2050</v>
+      </c>
+      <c r="D594" t="s">
+        <v>66</v>
+      </c>
+      <c r="E594">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="595" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A595" t="s">
+        <v>122</v>
+      </c>
+      <c r="B595" t="s">
+        <v>166</v>
+      </c>
+      <c r="C595">
+        <v>2050</v>
+      </c>
+      <c r="D595" t="s">
+        <v>67</v>
+      </c>
+      <c r="E595">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="596" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A596" t="s">
+        <v>122</v>
+      </c>
+      <c r="B596" t="s">
+        <v>167</v>
+      </c>
+      <c r="C596">
+        <v>2030</v>
+      </c>
+      <c r="D596" t="s">
+        <v>65</v>
+      </c>
+      <c r="E596">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="597" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A597" t="s">
+        <v>122</v>
+      </c>
+      <c r="B597" t="s">
+        <v>167</v>
+      </c>
+      <c r="C597">
+        <v>2030</v>
+      </c>
+      <c r="D597" t="s">
+        <v>66</v>
+      </c>
+      <c r="E597">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="598" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A598" t="s">
+        <v>122</v>
+      </c>
+      <c r="B598" t="s">
+        <v>167</v>
+      </c>
+      <c r="C598">
+        <v>2030</v>
+      </c>
+      <c r="D598" t="s">
+        <v>67</v>
+      </c>
+      <c r="E598">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="599" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A599" t="s">
+        <v>122</v>
+      </c>
+      <c r="B599" t="s">
+        <v>167</v>
+      </c>
+      <c r="C599">
+        <v>2050</v>
+      </c>
+      <c r="D599" t="s">
+        <v>65</v>
+      </c>
+      <c r="E599">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="600" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A600" t="s">
+        <v>122</v>
+      </c>
+      <c r="B600" t="s">
+        <v>167</v>
+      </c>
+      <c r="C600">
+        <v>2050</v>
+      </c>
+      <c r="D600" t="s">
+        <v>66</v>
+      </c>
+      <c r="E600">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="601" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A601" t="s">
+        <v>122</v>
+      </c>
+      <c r="B601" t="s">
+        <v>167</v>
+      </c>
+      <c r="C601">
+        <v>2050</v>
+      </c>
+      <c r="D601" t="s">
+        <v>67</v>
+      </c>
+      <c r="E601">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="602" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A602" t="s">
+        <v>122</v>
+      </c>
+      <c r="B602" t="s">
+        <v>168</v>
+      </c>
+      <c r="C602">
+        <v>2030</v>
+      </c>
+      <c r="D602" t="s">
+        <v>65</v>
+      </c>
+      <c r="E602">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="603" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A603" t="s">
+        <v>122</v>
+      </c>
+      <c r="B603" t="s">
+        <v>168</v>
+      </c>
+      <c r="C603">
+        <v>2030</v>
+      </c>
+      <c r="D603" t="s">
+        <v>66</v>
+      </c>
+      <c r="E603">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="604" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A604" t="s">
+        <v>122</v>
+      </c>
+      <c r="B604" t="s">
+        <v>168</v>
+      </c>
+      <c r="C604">
+        <v>2030</v>
+      </c>
+      <c r="D604" t="s">
+        <v>67</v>
+      </c>
+      <c r="E604">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="605" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A605" t="s">
+        <v>122</v>
+      </c>
+      <c r="B605" t="s">
+        <v>168</v>
+      </c>
+      <c r="C605">
+        <v>2050</v>
+      </c>
+      <c r="D605" t="s">
+        <v>65</v>
+      </c>
+      <c r="E605">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="606" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A606" t="s">
+        <v>122</v>
+      </c>
+      <c r="B606" t="s">
+        <v>168</v>
+      </c>
+      <c r="C606">
+        <v>2050</v>
+      </c>
+      <c r="D606" t="s">
+        <v>66</v>
+      </c>
+      <c r="E606">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="607" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A607" t="s">
+        <v>122</v>
+      </c>
+      <c r="B607" t="s">
+        <v>168</v>
+      </c>
+      <c r="C607">
+        <v>2050</v>
+      </c>
+      <c r="D607" t="s">
+        <v>67</v>
+      </c>
+      <c r="E607">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="608" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A608" t="s">
+        <v>122</v>
+      </c>
+      <c r="B608" t="s">
+        <v>169</v>
+      </c>
+      <c r="C608">
+        <v>2030</v>
+      </c>
+      <c r="D608" t="s">
+        <v>65</v>
+      </c>
+      <c r="E608">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="609" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A609" t="s">
+        <v>122</v>
+      </c>
+      <c r="B609" t="s">
+        <v>169</v>
+      </c>
+      <c r="C609">
+        <v>2030</v>
+      </c>
+      <c r="D609" t="s">
+        <v>66</v>
+      </c>
+      <c r="E609">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="610" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A610" t="s">
+        <v>122</v>
+      </c>
+      <c r="B610" t="s">
+        <v>169</v>
+      </c>
+      <c r="C610">
+        <v>2030</v>
+      </c>
+      <c r="D610" t="s">
+        <v>67</v>
+      </c>
+      <c r="E610">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="611" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A611" t="s">
+        <v>122</v>
+      </c>
+      <c r="B611" t="s">
+        <v>169</v>
+      </c>
+      <c r="C611">
+        <v>2050</v>
+      </c>
+      <c r="D611" t="s">
+        <v>65</v>
+      </c>
+      <c r="E611">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="612" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A612" t="s">
+        <v>122</v>
+      </c>
+      <c r="B612" t="s">
+        <v>169</v>
+      </c>
+      <c r="C612">
+        <v>2050</v>
+      </c>
+      <c r="D612" t="s">
+        <v>66</v>
+      </c>
+      <c r="E612">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="613" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A613" t="s">
+        <v>122</v>
+      </c>
+      <c r="B613" t="s">
+        <v>169</v>
+      </c>
+      <c r="C613">
+        <v>2050</v>
+      </c>
+      <c r="D613" t="s">
+        <v>67</v>
+      </c>
+      <c r="E613">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="614" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A614" t="s">
+        <v>122</v>
+      </c>
+      <c r="B614" t="s">
+        <v>170</v>
+      </c>
+      <c r="C614">
+        <v>2030</v>
+      </c>
+      <c r="D614" t="s">
+        <v>65</v>
+      </c>
+      <c r="E614">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="615" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A615" t="s">
+        <v>122</v>
+      </c>
+      <c r="B615" t="s">
+        <v>170</v>
+      </c>
+      <c r="C615">
+        <v>2030</v>
+      </c>
+      <c r="D615" t="s">
+        <v>66</v>
+      </c>
+      <c r="E615">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="616" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A616" t="s">
+        <v>122</v>
+      </c>
+      <c r="B616" t="s">
+        <v>170</v>
+      </c>
+      <c r="C616">
+        <v>2030</v>
+      </c>
+      <c r="D616" t="s">
+        <v>67</v>
+      </c>
+      <c r="E616">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="617" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A617" t="s">
+        <v>122</v>
+      </c>
+      <c r="B617" t="s">
+        <v>170</v>
+      </c>
+      <c r="C617">
+        <v>2050</v>
+      </c>
+      <c r="D617" t="s">
+        <v>65</v>
+      </c>
+      <c r="E617">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="618" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A618" t="s">
+        <v>122</v>
+      </c>
+      <c r="B618" t="s">
+        <v>170</v>
+      </c>
+      <c r="C618">
+        <v>2050</v>
+      </c>
+      <c r="D618" t="s">
+        <v>66</v>
+      </c>
+      <c r="E618">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="619" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A619" t="s">
+        <v>122</v>
+      </c>
+      <c r="B619" t="s">
+        <v>170</v>
+      </c>
+      <c r="C619">
+        <v>2050</v>
+      </c>
+      <c r="D619" t="s">
+        <v>67</v>
+      </c>
+      <c r="E619">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="620" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A620" t="s">
+        <v>122</v>
+      </c>
+      <c r="B620" t="s">
+        <v>171</v>
+      </c>
+      <c r="C620">
+        <v>2030</v>
+      </c>
+      <c r="D620" t="s">
+        <v>65</v>
+      </c>
+      <c r="E620">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="621" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A621" t="s">
+        <v>122</v>
+      </c>
+      <c r="B621" t="s">
+        <v>171</v>
+      </c>
+      <c r="C621">
+        <v>2030</v>
+      </c>
+      <c r="D621" t="s">
+        <v>66</v>
+      </c>
+      <c r="E621">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="622" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A622" t="s">
+        <v>122</v>
+      </c>
+      <c r="B622" t="s">
+        <v>171</v>
+      </c>
+      <c r="C622">
+        <v>2030</v>
+      </c>
+      <c r="D622" t="s">
+        <v>67</v>
+      </c>
+      <c r="E622">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="623" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A623" t="s">
+        <v>122</v>
+      </c>
+      <c r="B623" t="s">
+        <v>171</v>
+      </c>
+      <c r="C623">
+        <v>2050</v>
+      </c>
+      <c r="D623" t="s">
+        <v>65</v>
+      </c>
+      <c r="E623">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="624" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A624" t="s">
+        <v>122</v>
+      </c>
+      <c r="B624" t="s">
+        <v>171</v>
+      </c>
+      <c r="C624">
+        <v>2050</v>
+      </c>
+      <c r="D624" t="s">
+        <v>66</v>
+      </c>
+      <c r="E624">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="625" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A625" t="s">
+        <v>122</v>
+      </c>
+      <c r="B625" t="s">
+        <v>171</v>
+      </c>
+      <c r="C625">
+        <v>2050</v>
+      </c>
+      <c r="D625" t="s">
+        <v>67</v>
+      </c>
+      <c r="E625">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="626" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A626" t="s">
+        <v>122</v>
+      </c>
+      <c r="B626" t="s">
+        <v>172</v>
+      </c>
+      <c r="C626">
+        <v>2030</v>
+      </c>
+      <c r="D626" t="s">
+        <v>65</v>
+      </c>
+      <c r="E626">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="627" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A627" t="s">
+        <v>122</v>
+      </c>
+      <c r="B627" t="s">
+        <v>172</v>
+      </c>
+      <c r="C627">
+        <v>2030</v>
+      </c>
+      <c r="D627" t="s">
+        <v>66</v>
+      </c>
+      <c r="E627">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="628" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A628" t="s">
+        <v>122</v>
+      </c>
+      <c r="B628" t="s">
+        <v>172</v>
+      </c>
+      <c r="C628">
+        <v>2030</v>
+      </c>
+      <c r="D628" t="s">
+        <v>67</v>
+      </c>
+      <c r="E628">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="629" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A629" t="s">
+        <v>122</v>
+      </c>
+      <c r="B629" t="s">
+        <v>172</v>
+      </c>
+      <c r="C629">
+        <v>2050</v>
+      </c>
+      <c r="D629" t="s">
+        <v>65</v>
+      </c>
+      <c r="E629">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="630" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A630" t="s">
+        <v>122</v>
+      </c>
+      <c r="B630" t="s">
+        <v>172</v>
+      </c>
+      <c r="C630">
+        <v>2050</v>
+      </c>
+      <c r="D630" t="s">
+        <v>66</v>
+      </c>
+      <c r="E630">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="631" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A631" t="s">
+        <v>122</v>
+      </c>
+      <c r="B631" t="s">
+        <v>172</v>
+      </c>
+      <c r="C631">
+        <v>2050</v>
+      </c>
+      <c r="D631" t="s">
+        <v>67</v>
+      </c>
+      <c r="E631">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="632" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A632" t="s">
+        <v>63</v>
+      </c>
+      <c r="B632" t="s">
+        <v>173</v>
+      </c>
+      <c r="C632">
+        <v>2030</v>
+      </c>
+      <c r="D632" t="s">
+        <v>65</v>
+      </c>
+      <c r="E632">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="633" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A633" t="s">
+        <v>63</v>
+      </c>
+      <c r="B633" t="s">
+        <v>173</v>
+      </c>
+      <c r="C633">
+        <v>2030</v>
+      </c>
+      <c r="D633" t="s">
+        <v>66</v>
+      </c>
+      <c r="E633">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="634" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A634" t="s">
+        <v>63</v>
+      </c>
+      <c r="B634" t="s">
+        <v>173</v>
+      </c>
+      <c r="C634">
+        <v>2030</v>
+      </c>
+      <c r="D634" t="s">
+        <v>67</v>
+      </c>
+      <c r="E634">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="635" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A635" t="s">
+        <v>63</v>
+      </c>
+      <c r="B635" t="s">
+        <v>173</v>
+      </c>
+      <c r="C635">
+        <v>2050</v>
+      </c>
+      <c r="D635" t="s">
+        <v>65</v>
+      </c>
+      <c r="E635">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="636" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A636" t="s">
+        <v>63</v>
+      </c>
+      <c r="B636" t="s">
+        <v>173</v>
+      </c>
+      <c r="C636">
+        <v>2050</v>
+      </c>
+      <c r="D636" t="s">
+        <v>66</v>
+      </c>
+      <c r="E636">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="637" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A637" t="s">
+        <v>63</v>
+      </c>
+      <c r="B637" t="s">
+        <v>173</v>
+      </c>
+      <c r="C637">
+        <v>2050</v>
+      </c>
+      <c r="D637" t="s">
+        <v>67</v>
+      </c>
+      <c r="E637">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="638" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A638" t="s">
+        <v>122</v>
+      </c>
+      <c r="B638" t="s">
+        <v>174</v>
+      </c>
+      <c r="C638">
+        <v>2030</v>
+      </c>
+      <c r="D638" t="s">
+        <v>65</v>
+      </c>
+      <c r="E638">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="639" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A639" t="s">
+        <v>122</v>
+      </c>
+      <c r="B639" t="s">
+        <v>174</v>
+      </c>
+      <c r="C639">
+        <v>2030</v>
+      </c>
+      <c r="D639" t="s">
+        <v>66</v>
+      </c>
+      <c r="E639">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="640" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A640" t="s">
+        <v>122</v>
+      </c>
+      <c r="B640" t="s">
+        <v>174</v>
+      </c>
+      <c r="C640">
+        <v>2030</v>
+      </c>
+      <c r="D640" t="s">
+        <v>67</v>
+      </c>
+      <c r="E640">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="641" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A641" t="s">
+        <v>122</v>
+      </c>
+      <c r="B641" t="s">
+        <v>174</v>
+      </c>
+      <c r="C641">
+        <v>2050</v>
+      </c>
+      <c r="D641" t="s">
+        <v>65</v>
+      </c>
+      <c r="E641">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="642" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A642" t="s">
+        <v>122</v>
+      </c>
+      <c r="B642" t="s">
+        <v>174</v>
+      </c>
+      <c r="C642">
+        <v>2050</v>
+      </c>
+      <c r="D642" t="s">
+        <v>66</v>
+      </c>
+      <c r="E642">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="643" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A643" t="s">
+        <v>122</v>
+      </c>
+      <c r="B643" t="s">
+        <v>174</v>
+      </c>
+      <c r="C643">
+        <v>2050</v>
+      </c>
+      <c r="D643" t="s">
+        <v>67</v>
+      </c>
+      <c r="E643">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="644" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A644" t="s">
+        <v>122</v>
+      </c>
+      <c r="B644" t="s">
+        <v>175</v>
+      </c>
+      <c r="C644">
+        <v>2030</v>
+      </c>
+      <c r="D644" t="s">
+        <v>65</v>
+      </c>
+      <c r="E644">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="645" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A645" t="s">
+        <v>122</v>
+      </c>
+      <c r="B645" t="s">
+        <v>175</v>
+      </c>
+      <c r="C645">
+        <v>2030</v>
+      </c>
+      <c r="D645" t="s">
+        <v>66</v>
+      </c>
+      <c r="E645">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="646" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A646" t="s">
+        <v>122</v>
+      </c>
+      <c r="B646" t="s">
+        <v>175</v>
+      </c>
+      <c r="C646">
+        <v>2030</v>
+      </c>
+      <c r="D646" t="s">
+        <v>67</v>
+      </c>
+      <c r="E646">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="647" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A647" t="s">
+        <v>122</v>
+      </c>
+      <c r="B647" t="s">
+        <v>175</v>
+      </c>
+      <c r="C647">
+        <v>2050</v>
+      </c>
+      <c r="D647" t="s">
+        <v>65</v>
+      </c>
+      <c r="E647">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="648" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A648" t="s">
+        <v>122</v>
+      </c>
+      <c r="B648" t="s">
+        <v>175</v>
+      </c>
+      <c r="C648">
+        <v>2050</v>
+      </c>
+      <c r="D648" t="s">
+        <v>66</v>
+      </c>
+      <c r="E648">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="649" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A649" t="s">
+        <v>122</v>
+      </c>
+      <c r="B649" t="s">
+        <v>175</v>
+      </c>
+      <c r="C649">
+        <v>2050</v>
+      </c>
+      <c r="D649" t="s">
+        <v>67</v>
+      </c>
+      <c r="E649">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="650" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A650" t="s">
+        <v>122</v>
+      </c>
+      <c r="B650" t="s">
+        <v>176</v>
+      </c>
+      <c r="C650">
+        <v>2030</v>
+      </c>
+      <c r="D650" t="s">
+        <v>65</v>
+      </c>
+      <c r="E650">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="651" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A651" t="s">
+        <v>122</v>
+      </c>
+      <c r="B651" t="s">
+        <v>176</v>
+      </c>
+      <c r="C651">
+        <v>2030</v>
+      </c>
+      <c r="D651" t="s">
+        <v>66</v>
+      </c>
+      <c r="E651">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="652" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A652" t="s">
+        <v>122</v>
+      </c>
+      <c r="B652" t="s">
+        <v>176</v>
+      </c>
+      <c r="C652">
+        <v>2030</v>
+      </c>
+      <c r="D652" t="s">
+        <v>67</v>
+      </c>
+      <c r="E652">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="653" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A653" t="s">
+        <v>122</v>
+      </c>
+      <c r="B653" t="s">
+        <v>176</v>
+      </c>
+      <c r="C653">
+        <v>2050</v>
+      </c>
+      <c r="D653" t="s">
+        <v>65</v>
+      </c>
+      <c r="E653">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="654" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A654" t="s">
+        <v>122</v>
+      </c>
+      <c r="B654" t="s">
+        <v>176</v>
+      </c>
+      <c r="C654">
+        <v>2050</v>
+      </c>
+      <c r="D654" t="s">
+        <v>66</v>
+      </c>
+      <c r="E654">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="655" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A655" t="s">
+        <v>122</v>
+      </c>
+      <c r="B655" t="s">
+        <v>176</v>
+      </c>
+      <c r="C655">
+        <v>2050</v>
+      </c>
+      <c r="D655" t="s">
+        <v>67</v>
+      </c>
+      <c r="E655">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="656" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A656" t="s">
+        <v>122</v>
+      </c>
+      <c r="B656" t="s">
+        <v>177</v>
+      </c>
+      <c r="C656">
+        <v>2030</v>
+      </c>
+      <c r="D656" t="s">
+        <v>65</v>
+      </c>
+      <c r="E656">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="657" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A657" t="s">
+        <v>122</v>
+      </c>
+      <c r="B657" t="s">
+        <v>177</v>
+      </c>
+      <c r="C657">
+        <v>2030</v>
+      </c>
+      <c r="D657" t="s">
+        <v>66</v>
+      </c>
+      <c r="E657">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="658" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A658" t="s">
+        <v>122</v>
+      </c>
+      <c r="B658" t="s">
+        <v>177</v>
+      </c>
+      <c r="C658">
+        <v>2030</v>
+      </c>
+      <c r="D658" t="s">
+        <v>67</v>
+      </c>
+      <c r="E658">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="659" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A659" t="s">
+        <v>122</v>
+      </c>
+      <c r="B659" t="s">
+        <v>177</v>
+      </c>
+      <c r="C659">
+        <v>2050</v>
+      </c>
+      <c r="D659" t="s">
+        <v>65</v>
+      </c>
+      <c r="E659">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="660" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A660" t="s">
+        <v>122</v>
+      </c>
+      <c r="B660" t="s">
+        <v>177</v>
+      </c>
+      <c r="C660">
+        <v>2050</v>
+      </c>
+      <c r="D660" t="s">
+        <v>66</v>
+      </c>
+      <c r="E660">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="661" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A661" t="s">
+        <v>122</v>
+      </c>
+      <c r="B661" t="s">
+        <v>177</v>
+      </c>
+      <c r="C661">
+        <v>2050</v>
+      </c>
+      <c r="D661" t="s">
+        <v>67</v>
+      </c>
+      <c r="E661">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="662" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A662" t="s">
+        <v>122</v>
+      </c>
+      <c r="B662" t="s">
+        <v>178</v>
+      </c>
+      <c r="C662">
+        <v>2030</v>
+      </c>
+      <c r="D662" t="s">
+        <v>65</v>
+      </c>
+      <c r="E662">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="663" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A663" t="s">
+        <v>122</v>
+      </c>
+      <c r="B663" t="s">
+        <v>178</v>
+      </c>
+      <c r="C663">
+        <v>2030</v>
+      </c>
+      <c r="D663" t="s">
+        <v>66</v>
+      </c>
+      <c r="E663">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="664" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A664" t="s">
+        <v>122</v>
+      </c>
+      <c r="B664" t="s">
+        <v>178</v>
+      </c>
+      <c r="C664">
+        <v>2030</v>
+      </c>
+      <c r="D664" t="s">
+        <v>67</v>
+      </c>
+      <c r="E664">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="665" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A665" t="s">
+        <v>122</v>
+      </c>
+      <c r="B665" t="s">
+        <v>178</v>
+      </c>
+      <c r="C665">
+        <v>2050</v>
+      </c>
+      <c r="D665" t="s">
+        <v>65</v>
+      </c>
+      <c r="E665">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="666" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A666" t="s">
+        <v>122</v>
+      </c>
+      <c r="B666" t="s">
+        <v>178</v>
+      </c>
+      <c r="C666">
+        <v>2050</v>
+      </c>
+      <c r="D666" t="s">
+        <v>66</v>
+      </c>
+      <c r="E666">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="667" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A667" t="s">
+        <v>122</v>
+      </c>
+      <c r="B667" t="s">
+        <v>178</v>
+      </c>
+      <c r="C667">
+        <v>2050</v>
+      </c>
+      <c r="D667" t="s">
+        <v>67</v>
+      </c>
+      <c r="E667">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="668" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A668" t="s">
+        <v>122</v>
+      </c>
+      <c r="B668" t="s">
+        <v>179</v>
+      </c>
+      <c r="C668">
+        <v>2030</v>
+      </c>
+      <c r="D668" t="s">
+        <v>65</v>
+      </c>
+      <c r="E668">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="669" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A669" t="s">
+        <v>122</v>
+      </c>
+      <c r="B669" t="s">
+        <v>179</v>
+      </c>
+      <c r="C669">
+        <v>2030</v>
+      </c>
+      <c r="D669" t="s">
+        <v>66</v>
+      </c>
+      <c r="E669">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="670" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A670" t="s">
+        <v>122</v>
+      </c>
+      <c r="B670" t="s">
+        <v>179</v>
+      </c>
+      <c r="C670">
+        <v>2030</v>
+      </c>
+      <c r="D670" t="s">
+        <v>67</v>
+      </c>
+      <c r="E670">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="671" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A671" t="s">
+        <v>122</v>
+      </c>
+      <c r="B671" t="s">
+        <v>179</v>
+      </c>
+      <c r="C671">
+        <v>2050</v>
+      </c>
+      <c r="D671" t="s">
+        <v>65</v>
+      </c>
+      <c r="E671">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="672" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A672" t="s">
+        <v>122</v>
+      </c>
+      <c r="B672" t="s">
+        <v>179</v>
+      </c>
+      <c r="C672">
+        <v>2050</v>
+      </c>
+      <c r="D672" t="s">
+        <v>66</v>
+      </c>
+      <c r="E672">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="673" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A673" t="s">
+        <v>122</v>
+      </c>
+      <c r="B673" t="s">
+        <v>179</v>
+      </c>
+      <c r="C673">
+        <v>2050</v>
+      </c>
+      <c r="D673" t="s">
+        <v>67</v>
+      </c>
+      <c r="E673">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="674" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A674" t="s">
+        <v>122</v>
+      </c>
+      <c r="B674" t="s">
+        <v>180</v>
+      </c>
+      <c r="C674">
+        <v>2030</v>
+      </c>
+      <c r="D674" t="s">
+        <v>65</v>
+      </c>
+      <c r="E674">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="675" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A675" t="s">
+        <v>122</v>
+      </c>
+      <c r="B675" t="s">
+        <v>180</v>
+      </c>
+      <c r="C675">
+        <v>2030</v>
+      </c>
+      <c r="D675" t="s">
+        <v>66</v>
+      </c>
+      <c r="E675">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="676" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A676" t="s">
+        <v>122</v>
+      </c>
+      <c r="B676" t="s">
+        <v>180</v>
+      </c>
+      <c r="C676">
+        <v>2030</v>
+      </c>
+      <c r="D676" t="s">
+        <v>67</v>
+      </c>
+      <c r="E676">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="677" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A677" t="s">
+        <v>122</v>
+      </c>
+      <c r="B677" t="s">
+        <v>180</v>
+      </c>
+      <c r="C677">
+        <v>2050</v>
+      </c>
+      <c r="D677" t="s">
+        <v>65</v>
+      </c>
+      <c r="E677">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="678" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A678" t="s">
+        <v>122</v>
+      </c>
+      <c r="B678" t="s">
+        <v>180</v>
+      </c>
+      <c r="C678">
+        <v>2050</v>
+      </c>
+      <c r="D678" t="s">
+        <v>66</v>
+      </c>
+      <c r="E678">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="679" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A679" t="s">
+        <v>122</v>
+      </c>
+      <c r="B679" t="s">
+        <v>180</v>
+      </c>
+      <c r="C679">
+        <v>2050</v>
+      </c>
+      <c r="D679" t="s">
+        <v>67</v>
+      </c>
+      <c r="E679">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="680" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A680" t="s">
+        <v>122</v>
+      </c>
+      <c r="B680" t="s">
+        <v>181</v>
+      </c>
+      <c r="C680">
+        <v>2030</v>
+      </c>
+      <c r="D680" t="s">
+        <v>65</v>
+      </c>
+      <c r="E680">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="681" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A681" t="s">
+        <v>122</v>
+      </c>
+      <c r="B681" t="s">
+        <v>181</v>
+      </c>
+      <c r="C681">
+        <v>2030</v>
+      </c>
+      <c r="D681" t="s">
+        <v>66</v>
+      </c>
+      <c r="E681">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="682" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A682" t="s">
+        <v>122</v>
+      </c>
+      <c r="B682" t="s">
+        <v>181</v>
+      </c>
+      <c r="C682">
+        <v>2030</v>
+      </c>
+      <c r="D682" t="s">
+        <v>67</v>
+      </c>
+      <c r="E682">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="683" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A683" t="s">
+        <v>122</v>
+      </c>
+      <c r="B683" t="s">
+        <v>181</v>
+      </c>
+      <c r="C683">
+        <v>2050</v>
+      </c>
+      <c r="D683" t="s">
+        <v>65</v>
+      </c>
+      <c r="E683">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="684" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A684" t="s">
+        <v>122</v>
+      </c>
+      <c r="B684" t="s">
+        <v>181</v>
+      </c>
+      <c r="C684">
+        <v>2050</v>
+      </c>
+      <c r="D684" t="s">
+        <v>66</v>
+      </c>
+      <c r="E684">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="685" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A685" t="s">
+        <v>122</v>
+      </c>
+      <c r="B685" t="s">
+        <v>181</v>
+      </c>
+      <c r="C685">
+        <v>2050</v>
+      </c>
+      <c r="D685" t="s">
+        <v>67</v>
+      </c>
+      <c r="E685">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="686" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A686" t="s">
+        <v>122</v>
+      </c>
+      <c r="B686" t="s">
+        <v>182</v>
+      </c>
+      <c r="C686">
+        <v>2030</v>
+      </c>
+      <c r="D686" t="s">
+        <v>65</v>
+      </c>
+      <c r="E686">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="687" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A687" t="s">
+        <v>122</v>
+      </c>
+      <c r="B687" t="s">
+        <v>182</v>
+      </c>
+      <c r="C687">
+        <v>2030</v>
+      </c>
+      <c r="D687" t="s">
+        <v>66</v>
+      </c>
+      <c r="E687">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="688" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A688" t="s">
+        <v>122</v>
+      </c>
+      <c r="B688" t="s">
+        <v>182</v>
+      </c>
+      <c r="C688">
+        <v>2030</v>
+      </c>
+      <c r="D688" t="s">
+        <v>67</v>
+      </c>
+      <c r="E688">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="689" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A689" t="s">
+        <v>122</v>
+      </c>
+      <c r="B689" t="s">
+        <v>182</v>
+      </c>
+      <c r="C689">
+        <v>2050</v>
+      </c>
+      <c r="D689" t="s">
+        <v>65</v>
+      </c>
+      <c r="E689">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="690" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A690" t="s">
+        <v>122</v>
+      </c>
+      <c r="B690" t="s">
+        <v>182</v>
+      </c>
+      <c r="C690">
+        <v>2050</v>
+      </c>
+      <c r="D690" t="s">
+        <v>66</v>
+      </c>
+      <c r="E690">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="691" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A691" t="s">
+        <v>122</v>
+      </c>
+      <c r="B691" t="s">
+        <v>182</v>
+      </c>
+      <c r="C691">
+        <v>2050</v>
+      </c>
+      <c r="D691" t="s">
+        <v>67</v>
+      </c>
+      <c r="E691">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="692" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A692" t="s">
+        <v>63</v>
+      </c>
+      <c r="B692" t="s">
+        <v>183</v>
+      </c>
+      <c r="C692">
+        <v>2030</v>
+      </c>
+      <c r="D692" t="s">
+        <v>65</v>
+      </c>
+      <c r="E692">
+        <v>0</v>
+      </c>
+      <c r="R692">
+        <v>5.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="693" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A693" t="s">
+        <v>63</v>
+      </c>
+      <c r="B693" t="s">
+        <v>183</v>
+      </c>
+      <c r="C693">
+        <v>2030</v>
+      </c>
+      <c r="D693" t="s">
+        <v>66</v>
+      </c>
+      <c r="E693">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="694" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A694" t="s">
+        <v>63</v>
+      </c>
+      <c r="B694" t="s">
+        <v>183</v>
+      </c>
+      <c r="C694">
+        <v>2030</v>
+      </c>
+      <c r="D694" t="s">
+        <v>67</v>
+      </c>
+      <c r="E694">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="695" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A695" t="s">
+        <v>63</v>
+      </c>
+      <c r="B695" t="s">
+        <v>183</v>
+      </c>
+      <c r="C695">
+        <v>2050</v>
+      </c>
+      <c r="D695" t="s">
+        <v>65</v>
+      </c>
+      <c r="E695">
+        <v>0</v>
+      </c>
+      <c r="R695">
+        <v>5.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="696" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A696" t="s">
+        <v>63</v>
+      </c>
+      <c r="B696" t="s">
+        <v>183</v>
+      </c>
+      <c r="C696">
+        <v>2050</v>
+      </c>
+      <c r="D696" t="s">
+        <v>66</v>
+      </c>
+      <c r="E696">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="697" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A697" t="s">
+        <v>63</v>
+      </c>
+      <c r="B697" t="s">
+        <v>183</v>
+      </c>
+      <c r="C697">
+        <v>2050</v>
+      </c>
+      <c r="D697" t="s">
+        <v>67</v>
+      </c>
+      <c r="E697">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="698" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A698" t="s">
+        <v>122</v>
+      </c>
+      <c r="B698" t="s">
+        <v>184</v>
+      </c>
+      <c r="C698">
+        <v>2030</v>
+      </c>
+      <c r="D698" t="s">
+        <v>65</v>
+      </c>
+      <c r="E698">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="699" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A699" t="s">
+        <v>122</v>
+      </c>
+      <c r="B699" t="s">
+        <v>184</v>
+      </c>
+      <c r="C699">
+        <v>2030</v>
+      </c>
+      <c r="D699" t="s">
+        <v>66</v>
+      </c>
+      <c r="E699">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="700" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A700" t="s">
+        <v>122</v>
+      </c>
+      <c r="B700" t="s">
+        <v>184</v>
+      </c>
+      <c r="C700">
+        <v>2030</v>
+      </c>
+      <c r="D700" t="s">
+        <v>67</v>
+      </c>
+      <c r="E700">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="701" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A701" t="s">
+        <v>122</v>
+      </c>
+      <c r="B701" t="s">
+        <v>184</v>
+      </c>
+      <c r="C701">
+        <v>2050</v>
+      </c>
+      <c r="D701" t="s">
+        <v>65</v>
+      </c>
+      <c r="E701">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="702" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A702" t="s">
+        <v>122</v>
+      </c>
+      <c r="B702" t="s">
+        <v>184</v>
+      </c>
+      <c r="C702">
+        <v>2050</v>
+      </c>
+      <c r="D702" t="s">
+        <v>66</v>
+      </c>
+      <c r="E702">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="703" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A703" t="s">
+        <v>122</v>
+      </c>
+      <c r="B703" t="s">
+        <v>184</v>
+      </c>
+      <c r="C703">
+        <v>2050</v>
+      </c>
+      <c r="D703" t="s">
+        <v>67</v>
+      </c>
+      <c r="E703">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="704" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A704" t="s">
+        <v>122</v>
+      </c>
+      <c r="B704" t="s">
+        <v>185</v>
+      </c>
+      <c r="C704">
+        <v>2030</v>
+      </c>
+      <c r="D704" t="s">
+        <v>65</v>
+      </c>
+      <c r="E704">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="705" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A705" t="s">
+        <v>122</v>
+      </c>
+      <c r="B705" t="s">
+        <v>185</v>
+      </c>
+      <c r="C705">
+        <v>2030</v>
+      </c>
+      <c r="D705" t="s">
+        <v>66</v>
+      </c>
+      <c r="E705">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="706" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A706" t="s">
+        <v>122</v>
+      </c>
+      <c r="B706" t="s">
+        <v>185</v>
+      </c>
+      <c r="C706">
+        <v>2030</v>
+      </c>
+      <c r="D706" t="s">
+        <v>67</v>
+      </c>
+      <c r="E706">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="707" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A707" t="s">
+        <v>122</v>
+      </c>
+      <c r="B707" t="s">
+        <v>185</v>
+      </c>
+      <c r="C707">
+        <v>2050</v>
+      </c>
+      <c r="D707" t="s">
+        <v>65</v>
+      </c>
+      <c r="E707">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="708" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A708" t="s">
+        <v>122</v>
+      </c>
+      <c r="B708" t="s">
+        <v>185</v>
+      </c>
+      <c r="C708">
+        <v>2050</v>
+      </c>
+      <c r="D708" t="s">
+        <v>66</v>
+      </c>
+      <c r="E708">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="709" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A709" t="s">
+        <v>122</v>
+      </c>
+      <c r="B709" t="s">
+        <v>185</v>
+      </c>
+      <c r="C709">
+        <v>2050</v>
+      </c>
+      <c r="D709" t="s">
+        <v>67</v>
+      </c>
+      <c r="E709">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="710" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A710" t="s">
+        <v>122</v>
+      </c>
+      <c r="B710" t="s">
+        <v>186</v>
+      </c>
+      <c r="C710">
+        <v>2030</v>
+      </c>
+      <c r="D710" t="s">
+        <v>65</v>
+      </c>
+      <c r="E710">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="711" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A711" t="s">
+        <v>122</v>
+      </c>
+      <c r="B711" t="s">
+        <v>186</v>
+      </c>
+      <c r="C711">
+        <v>2030</v>
+      </c>
+      <c r="D711" t="s">
+        <v>66</v>
+      </c>
+      <c r="E711">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="712" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A712" t="s">
+        <v>122</v>
+      </c>
+      <c r="B712" t="s">
+        <v>186</v>
+      </c>
+      <c r="C712">
+        <v>2030</v>
+      </c>
+      <c r="D712" t="s">
+        <v>67</v>
+      </c>
+      <c r="E712">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="713" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A713" t="s">
+        <v>122</v>
+      </c>
+      <c r="B713" t="s">
+        <v>186</v>
+      </c>
+      <c r="C713">
+        <v>2050</v>
+      </c>
+      <c r="D713" t="s">
+        <v>65</v>
+      </c>
+      <c r="E713">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="714" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A714" t="s">
+        <v>122</v>
+      </c>
+      <c r="B714" t="s">
+        <v>186</v>
+      </c>
+      <c r="C714">
+        <v>2050</v>
+      </c>
+      <c r="D714" t="s">
+        <v>66</v>
+      </c>
+      <c r="E714">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="715" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A715" t="s">
+        <v>122</v>
+      </c>
+      <c r="B715" t="s">
+        <v>186</v>
+      </c>
+      <c r="C715">
+        <v>2050</v>
+      </c>
+      <c r="D715" t="s">
+        <v>67</v>
+      </c>
+      <c r="E715">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="716" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A716" t="s">
+        <v>122</v>
+      </c>
+      <c r="B716" t="s">
+        <v>187</v>
+      </c>
+      <c r="C716">
+        <v>2030</v>
+      </c>
+      <c r="D716" t="s">
+        <v>65</v>
+      </c>
+      <c r="E716">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="717" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A717" t="s">
+        <v>122</v>
+      </c>
+      <c r="B717" t="s">
+        <v>187</v>
+      </c>
+      <c r="C717">
+        <v>2030</v>
+      </c>
+      <c r="D717" t="s">
+        <v>66</v>
+      </c>
+      <c r="E717">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="718" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A718" t="s">
+        <v>122</v>
+      </c>
+      <c r="B718" t="s">
+        <v>187</v>
+      </c>
+      <c r="C718">
+        <v>2030</v>
+      </c>
+      <c r="D718" t="s">
+        <v>67</v>
+      </c>
+      <c r="E718">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="719" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A719" t="s">
+        <v>122</v>
+      </c>
+      <c r="B719" t="s">
+        <v>187</v>
+      </c>
+      <c r="C719">
+        <v>2050</v>
+      </c>
+      <c r="D719" t="s">
+        <v>65</v>
+      </c>
+      <c r="E719">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="720" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A720" t="s">
+        <v>122</v>
+      </c>
+      <c r="B720" t="s">
+        <v>187</v>
+      </c>
+      <c r="C720">
+        <v>2050</v>
+      </c>
+      <c r="D720" t="s">
+        <v>66</v>
+      </c>
+      <c r="E720">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="721" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A721" t="s">
+        <v>122</v>
+      </c>
+      <c r="B721" t="s">
+        <v>187</v>
+      </c>
+      <c r="C721">
+        <v>2050</v>
+      </c>
+      <c r="D721" t="s">
+        <v>67</v>
+      </c>
+      <c r="E721">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="722" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A722" t="s">
+        <v>122</v>
+      </c>
+      <c r="B722" t="s">
+        <v>188</v>
+      </c>
+      <c r="C722">
+        <v>2030</v>
+      </c>
+      <c r="D722" t="s">
+        <v>65</v>
+      </c>
+      <c r="E722">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="723" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A723" t="s">
+        <v>122</v>
+      </c>
+      <c r="B723" t="s">
+        <v>188</v>
+      </c>
+      <c r="C723">
+        <v>2030</v>
+      </c>
+      <c r="D723" t="s">
+        <v>66</v>
+      </c>
+      <c r="E723">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="724" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A724" t="s">
+        <v>122</v>
+      </c>
+      <c r="B724" t="s">
+        <v>188</v>
+      </c>
+      <c r="C724">
+        <v>2030</v>
+      </c>
+      <c r="D724" t="s">
+        <v>67</v>
+      </c>
+      <c r="E724">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="725" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A725" t="s">
+        <v>122</v>
+      </c>
+      <c r="B725" t="s">
+        <v>188</v>
+      </c>
+      <c r="C725">
+        <v>2050</v>
+      </c>
+      <c r="D725" t="s">
+        <v>65</v>
+      </c>
+      <c r="E725">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="726" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A726" t="s">
+        <v>122</v>
+      </c>
+      <c r="B726" t="s">
+        <v>188</v>
+      </c>
+      <c r="C726">
+        <v>2050</v>
+      </c>
+      <c r="D726" t="s">
+        <v>66</v>
+      </c>
+      <c r="E726">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="727" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A727" t="s">
+        <v>122</v>
+      </c>
+      <c r="B727" t="s">
+        <v>188</v>
+      </c>
+      <c r="C727">
+        <v>2050</v>
+      </c>
+      <c r="D727" t="s">
+        <v>67</v>
+      </c>
+      <c r="E727">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="728" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A728" t="s">
+        <v>122</v>
+      </c>
+      <c r="B728" t="s">
+        <v>189</v>
+      </c>
+      <c r="C728">
+        <v>2030</v>
+      </c>
+      <c r="D728" t="s">
+        <v>65</v>
+      </c>
+      <c r="E728">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="729" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A729" t="s">
+        <v>122</v>
+      </c>
+      <c r="B729" t="s">
+        <v>189</v>
+      </c>
+      <c r="C729">
+        <v>2030</v>
+      </c>
+      <c r="D729" t="s">
+        <v>66</v>
+      </c>
+      <c r="E729">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="730" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A730" t="s">
+        <v>122</v>
+      </c>
+      <c r="B730" t="s">
+        <v>189</v>
+      </c>
+      <c r="C730">
+        <v>2030</v>
+      </c>
+      <c r="D730" t="s">
+        <v>67</v>
+      </c>
+      <c r="E730">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="731" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A731" t="s">
+        <v>122</v>
+      </c>
+      <c r="B731" t="s">
+        <v>189</v>
+      </c>
+      <c r="C731">
+        <v>2050</v>
+      </c>
+      <c r="D731" t="s">
+        <v>65</v>
+      </c>
+      <c r="E731">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="732" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A732" t="s">
+        <v>122</v>
+      </c>
+      <c r="B732" t="s">
+        <v>189</v>
+      </c>
+      <c r="C732">
+        <v>2050</v>
+      </c>
+      <c r="D732" t="s">
+        <v>66</v>
+      </c>
+      <c r="E732">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="733" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A733" t="s">
+        <v>122</v>
+      </c>
+      <c r="B733" t="s">
+        <v>189</v>
+      </c>
+      <c r="C733">
+        <v>2050</v>
+      </c>
+      <c r="D733" t="s">
+        <v>67</v>
+      </c>
+      <c r="E733">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="734" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A734" t="s">
+        <v>122</v>
+      </c>
+      <c r="B734" t="s">
+        <v>190</v>
+      </c>
+      <c r="C734">
+        <v>2030</v>
+      </c>
+      <c r="D734" t="s">
+        <v>65</v>
+      </c>
+      <c r="E734">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="735" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A735" t="s">
+        <v>122</v>
+      </c>
+      <c r="B735" t="s">
+        <v>190</v>
+      </c>
+      <c r="C735">
+        <v>2030</v>
+      </c>
+      <c r="D735" t="s">
+        <v>66</v>
+      </c>
+      <c r="E735">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="736" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A736" t="s">
+        <v>122</v>
+      </c>
+      <c r="B736" t="s">
+        <v>190</v>
+      </c>
+      <c r="C736">
+        <v>2030</v>
+      </c>
+      <c r="D736" t="s">
+        <v>67</v>
+      </c>
+      <c r="E736">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="737" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A737" t="s">
+        <v>122</v>
+      </c>
+      <c r="B737" t="s">
+        <v>190</v>
+      </c>
+      <c r="C737">
+        <v>2050</v>
+      </c>
+      <c r="D737" t="s">
+        <v>65</v>
+      </c>
+      <c r="E737">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="738" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A738" t="s">
+        <v>122</v>
+      </c>
+      <c r="B738" t="s">
+        <v>190</v>
+      </c>
+      <c r="C738">
+        <v>2050</v>
+      </c>
+      <c r="D738" t="s">
+        <v>66</v>
+      </c>
+      <c r="E738">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="739" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A739" t="s">
+        <v>122</v>
+      </c>
+      <c r="B739" t="s">
+        <v>190</v>
+      </c>
+      <c r="C739">
+        <v>2050</v>
+      </c>
+      <c r="D739" t="s">
+        <v>67</v>
+      </c>
+      <c r="E739">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="740" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A740" t="s">
+        <v>122</v>
+      </c>
+      <c r="B740" t="s">
+        <v>191</v>
+      </c>
+      <c r="C740">
+        <v>2030</v>
+      </c>
+      <c r="D740" t="s">
+        <v>65</v>
+      </c>
+      <c r="E740">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="741" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A741" t="s">
+        <v>122</v>
+      </c>
+      <c r="B741" t="s">
+        <v>191</v>
+      </c>
+      <c r="C741">
+        <v>2030</v>
+      </c>
+      <c r="D741" t="s">
+        <v>66</v>
+      </c>
+      <c r="E741">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="742" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A742" t="s">
+        <v>122</v>
+      </c>
+      <c r="B742" t="s">
+        <v>191</v>
+      </c>
+      <c r="C742">
+        <v>2030</v>
+      </c>
+      <c r="D742" t="s">
+        <v>67</v>
+      </c>
+      <c r="E742">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="743" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A743" t="s">
+        <v>122</v>
+      </c>
+      <c r="B743" t="s">
+        <v>191</v>
+      </c>
+      <c r="C743">
+        <v>2050</v>
+      </c>
+      <c r="D743" t="s">
+        <v>65</v>
+      </c>
+      <c r="E743">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="744" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A744" t="s">
+        <v>122</v>
+      </c>
+      <c r="B744" t="s">
+        <v>191</v>
+      </c>
+      <c r="C744">
+        <v>2050</v>
+      </c>
+      <c r="D744" t="s">
+        <v>66</v>
+      </c>
+      <c r="E744">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="745" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A745" t="s">
+        <v>122</v>
+      </c>
+      <c r="B745" t="s">
+        <v>191</v>
+      </c>
+      <c r="C745">
+        <v>2050</v>
+      </c>
+      <c r="D745" t="s">
+        <v>67</v>
+      </c>
+      <c r="E745">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="746" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A746" t="s">
+        <v>122</v>
+      </c>
+      <c r="B746" t="s">
+        <v>192</v>
+      </c>
+      <c r="C746">
+        <v>2030</v>
+      </c>
+      <c r="D746" t="s">
+        <v>65</v>
+      </c>
+      <c r="E746">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="747" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A747" t="s">
+        <v>122</v>
+      </c>
+      <c r="B747" t="s">
+        <v>192</v>
+      </c>
+      <c r="C747">
+        <v>2030</v>
+      </c>
+      <c r="D747" t="s">
+        <v>66</v>
+      </c>
+      <c r="E747">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="748" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A748" t="s">
+        <v>122</v>
+      </c>
+      <c r="B748" t="s">
+        <v>192</v>
+      </c>
+      <c r="C748">
+        <v>2030</v>
+      </c>
+      <c r="D748" t="s">
+        <v>67</v>
+      </c>
+      <c r="E748">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="749" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A749" t="s">
+        <v>122</v>
+      </c>
+      <c r="B749" t="s">
+        <v>192</v>
+      </c>
+      <c r="C749">
+        <v>2050</v>
+      </c>
+      <c r="D749" t="s">
+        <v>65</v>
+      </c>
+      <c r="E749">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="750" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A750" t="s">
+        <v>122</v>
+      </c>
+      <c r="B750" t="s">
+        <v>192</v>
+      </c>
+      <c r="C750">
+        <v>2050</v>
+      </c>
+      <c r="D750" t="s">
+        <v>66</v>
+      </c>
+      <c r="E750">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="751" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A751" t="s">
+        <v>122</v>
+      </c>
+      <c r="B751" t="s">
+        <v>192</v>
+      </c>
+      <c r="C751">
+        <v>2050</v>
+      </c>
+      <c r="D751" t="s">
+        <v>67</v>
+      </c>
+      <c r="E751">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:D751" xr:uid="{4E24C6E2-DFBD-4ECB-B058-D278CB417CB7}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="sc_a"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>